--- a/Human-JAVA/Human_11m_project/1108JavaTASK.xlsx
+++ b/Human-JAVA/Human_11m_project/1108JavaTASK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuuri/Study/Human-JAVA/프로젝트PPT자료/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F26A3B5-5CD5-6046-9C6B-3C2B8B7FA200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90427945-286D-4141-9CE7-1274718CF80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="487">
   <si>
     <t>패키지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3778,6 +3778,83 @@
         <charset val="129"/>
       </rPr>
       <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> -&gt;  SELECT * FROM Book;SELECT * FROM Book;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT rnum AS Review_Number , book AS TITLE , rtext AS Review , rec AS Recommend , M.name AS NAME</t>
+  </si>
+  <si>
+    <t>FROM Review R, Members M </t>
+  </si>
+  <si>
+    <r>
+      <t>WHERE R.id = M.id AND R.book LIKE '%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키워드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>%';</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT name , id , point FROM Members WHERE name = '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유저이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>';</t>
     </r>
   </si>
 </sst>
@@ -3792,7 +3869,7 @@
     <numFmt numFmtId="179" formatCode="@\,"/>
     <numFmt numFmtId="180" formatCode="\,\'@\'\,"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -3907,6 +3984,27 @@
     <font>
       <sz val="18"/>
       <color rgb="FF669768"/>
+      <name val="D2Coding ligature"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Apple SD Gothic Neo"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="D2Coding ligature"/>
       <family val="2"/>
       <charset val="129"/>
@@ -4031,7 +4129,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4154,6 +4252,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6925,10 +7038,12 @@
         <v>170</v>
       </c>
       <c r="G210" s="32"/>
-      <c r="K210" s="3" t="s">
+      <c r="K210" s="42" t="s">
         <v>423</v>
       </c>
-      <c r="L210" s="23"/>
+      <c r="L210" s="43" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="211" spans="5:12">
       <c r="E211" s="8" t="s">
@@ -6941,6 +7056,9 @@
       <c r="K211" s="24" t="s">
         <v>424</v>
       </c>
+      <c r="L211" s="41" t="s">
+        <v>483</v>
+      </c>
     </row>
     <row r="212" spans="5:12">
       <c r="E212" s="8" t="s">
@@ -6953,6 +7071,9 @@
       <c r="K212" s="24" t="s">
         <v>445</v>
       </c>
+      <c r="L212" s="41" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="213" spans="5:12">
       <c r="E213" s="8" t="s">
@@ -6965,6 +7086,9 @@
       <c r="K213" s="24" t="s">
         <v>425</v>
       </c>
+      <c r="L213" s="41" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="215" spans="5:12">
       <c r="E215" s="11" t="s">
@@ -7018,8 +7142,11 @@
       </c>
     </row>
     <row r="219" spans="5:12">
-      <c r="K219" s="3" t="s">
+      <c r="K219" s="44" t="s">
         <v>428</v>
+      </c>
+      <c r="L219" s="45" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="5:12">

--- a/Human-JAVA/Human_11m_project/1108JavaTASK.xlsx
+++ b/Human-JAVA/Human_11m_project/1108JavaTASK.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuuri/Study/Human-JAVA/프로젝트PPT자료/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuuri/Study/Human-JAVA/Human_11m_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90427945-286D-4141-9CE7-1274718CF80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7363B130-AEE3-4744-A47D-63C8F7A47922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="2" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="490">
   <si>
     <t>패키지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1698,62 +1698,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
     <t>쿼리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1770,1610 +1714,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>CREATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Members</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>PRIMARY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>KEY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>pw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>) ,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>point</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CREATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>PRIMARY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>KEY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>author</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>rec</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>create</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>table</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Review</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>rnum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>primary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>rtext</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>rec</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>CHECK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>rec</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>IN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>wdate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>timestamp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>sysdate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>foreign</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>REFERENCES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>cascade</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>foreign</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>references</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Members</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>set</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>null</t>
-    </r>
-  </si>
-  <si>
     <t>/*</t>
   </si>
   <si>
@@ -3381,404 +1721,6 @@
   </si>
   <si>
     <t>*/</t>
-  </si>
-  <si>
-    <r>
-      <t>CREATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>SEQUENCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Review_no</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>INCREMENT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>BY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFC0C0C0"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Members</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FF739ECA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Review</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DROP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Review</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DROP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DROP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFC1AA6C"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFAAAAAA"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF9E9E9E"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>Members</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FFEECC64"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>;</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve"> -&gt;  SELECT * FROM Book;SELECT * FROM Book;</t>
@@ -3856,6 +1798,1264 @@
       </rPr>
       <t>';</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">id </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(10) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pw </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10) ,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">name </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">point </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(10) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">book </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(30) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">author </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rec </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(3) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>create</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rnum </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(30) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">book </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(30),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rtext </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(500),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rec </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(1) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>CHECK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (rec </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>IN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(0, 1));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">id </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">wdate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>timestamp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>sysdate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>foreign</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (book) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book(book) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>cascade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>foreign</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>references</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members(id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>null</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>SEQUENCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review_no </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>INCREMENT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 1;</t>
+    </r>
+  </si>
+  <si>
+    <t>admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3869,7 +3069,7 @@
     <numFmt numFmtId="179" formatCode="@\,"/>
     <numFmt numFmtId="180" formatCode="\,\'@\'\,"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="13">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -3938,57 +3138,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color rgb="FFAAAAAA"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF739ECA"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF9E9E9E"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FFEECC64"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFC1AA6C"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FFC0C0C0"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF669768"/>
-      <name val="D2Coding ligature"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
@@ -4003,6 +3152,13 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="D2Coding ligature"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="D2Coding ligature"/>
@@ -4129,7 +3285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4199,9 +3355,6 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -4214,31 +3367,25 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4250,23 +3397,38 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4625,363 +3787,363 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="37">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35" t="s">
+      <c r="C4" s="33"/>
+      <c r="D4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="35"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="35"/>
+      <c r="H4" s="33"/>
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35" t="s">
+      <c r="C5" s="33"/>
+      <c r="D5" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="16" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="35"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="16" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35" t="s">
+      <c r="C7" s="33"/>
+      <c r="D7" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="35"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="16" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="33"/>
+      <c r="D8" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="16"/>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35" t="s">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="33"/>
       <c r="F12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="33"/>
       <c r="I12" s="16"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35" t="s">
+      <c r="C13" s="33"/>
+      <c r="D13" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="33"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35" t="s">
+      <c r="C14" s="33"/>
+      <c r="D14" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E14" s="35"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="16" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="16"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36" t="s">
+      <c r="C17" s="32"/>
+      <c r="D17" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
       <c r="I17" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35" t="s">
+      <c r="C18" s="33"/>
+      <c r="D18" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="35"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35" t="s">
+      <c r="C19" s="33"/>
+      <c r="D19" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="35"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="16"/>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="16" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35" t="s">
+      <c r="C20" s="33"/>
+      <c r="D20" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="35"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35" t="s">
+      <c r="C21" s="33"/>
+      <c r="D21" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="E21" s="35"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="16"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
       <c r="I21" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35" t="s">
+      <c r="C22" s="33"/>
+      <c r="D22" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="35"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="16"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
       <c r="I22" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35" t="s">
+      <c r="C23" s="33"/>
+      <c r="D23" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="35"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="H23" s="35"/>
+      <c r="H23" s="33"/>
       <c r="I23" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35" t="s">
+      <c r="C24" s="33"/>
+      <c r="D24" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="35"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="16"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
       <c r="I24" s="16" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="37">
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="37" t="s">
+      <c r="B34" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="41"/>
+      <c r="D34" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="38"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="35"/>
       <c r="I34" s="4" t="s">
         <v>1</v>
       </c>
@@ -5019,13 +4181,13 @@
       <c r="C36" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="34" t="s">
+      <c r="D36" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
       <c r="I36" s="9" t="s">
         <v>12</v>
       </c>
@@ -5037,13 +4199,13 @@
       <c r="C37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
       <c r="I37" s="9" t="s">
         <v>156</v>
       </c>
@@ -5052,17 +4214,17 @@
       <c r="C38" s="17"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="37" t="s">
+      <c r="B39" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="41"/>
+      <c r="D39" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="38"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="35"/>
       <c r="I39" s="4" t="s">
         <v>1</v>
       </c>
@@ -5100,13 +4262,13 @@
       <c r="C41" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="34" t="s">
+      <c r="D41" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
       <c r="I41" s="9"/>
     </row>
     <row r="42" spans="2:9">
@@ -5182,31 +4344,31 @@
       <c r="C55" s="17"/>
     </row>
     <row r="58" spans="2:9">
-      <c r="B58" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C58" s="38"/>
-      <c r="D58" s="37" t="s">
+      <c r="B58" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="35"/>
+      <c r="D58" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="38"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="35"/>
       <c r="I58" s="10"/>
     </row>
     <row r="59" spans="2:9">
-      <c r="B59" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="38"/>
-      <c r="D59" s="37" t="s">
+      <c r="B59" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="35"/>
+      <c r="D59" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="38"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="35"/>
       <c r="I59" s="10"/>
     </row>
     <row r="60" spans="2:9">
@@ -5238,11 +4400,11 @@
     <row r="61" spans="2:9">
       <c r="B61" s="6"/>
       <c r="C61" s="7"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="34"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="37"/>
       <c r="I61" s="9"/>
     </row>
     <row r="62" spans="2:9">
@@ -5336,31 +4498,31 @@
       <c r="I70" s="9"/>
     </row>
     <row r="74" spans="2:9">
-      <c r="B74" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C74" s="38"/>
-      <c r="D74" s="37" t="s">
+      <c r="B74" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="35"/>
+      <c r="D74" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="38"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="35"/>
       <c r="I74" s="10"/>
     </row>
     <row r="75" spans="2:9">
-      <c r="B75" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C75" s="38"/>
-      <c r="D75" s="37" t="s">
+      <c r="B75" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="35"/>
+      <c r="D75" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="38"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="35"/>
       <c r="I75" s="10"/>
     </row>
     <row r="76" spans="2:9" s="1" customFormat="1">
@@ -5396,13 +4558,13 @@
       <c r="C77" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D77" s="34" t="s">
+      <c r="D77" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="34"/>
-      <c r="H77" s="34"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
       <c r="I77" s="9" t="s">
         <v>27</v>
       </c>
@@ -5728,31 +4890,31 @@
       </c>
     </row>
     <row r="95" spans="2:9">
-      <c r="B95" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C95" s="38"/>
-      <c r="D95" s="37" t="s">
+      <c r="B95" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C95" s="35"/>
+      <c r="D95" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E95" s="39"/>
-      <c r="F95" s="39"/>
-      <c r="G95" s="39"/>
-      <c r="H95" s="38"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+      <c r="G95" s="36"/>
+      <c r="H95" s="35"/>
       <c r="I95" s="10"/>
     </row>
     <row r="96" spans="2:9">
-      <c r="B96" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C96" s="38"/>
-      <c r="D96" s="37" t="s">
+      <c r="B96" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" s="35"/>
+      <c r="D96" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="39"/>
-      <c r="F96" s="39"/>
-      <c r="G96" s="39"/>
-      <c r="H96" s="38"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="36"/>
+      <c r="G96" s="36"/>
+      <c r="H96" s="35"/>
       <c r="I96" s="10"/>
     </row>
     <row r="97" spans="2:9" s="1" customFormat="1">
@@ -5788,13 +4950,13 @@
       <c r="C98" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D98" s="34" t="s">
+      <c r="D98" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E98" s="34"/>
-      <c r="F98" s="34"/>
-      <c r="G98" s="34"/>
-      <c r="H98" s="34"/>
+      <c r="E98" s="37"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="37"/>
+      <c r="H98" s="37"/>
       <c r="I98" s="9" t="s">
         <v>51</v>
       </c>
@@ -5858,31 +5020,31 @@
       </c>
     </row>
     <row r="104" spans="2:9">
-      <c r="B104" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="38"/>
-      <c r="D104" s="37" t="s">
+      <c r="B104" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="35"/>
+      <c r="D104" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E104" s="39"/>
-      <c r="F104" s="39"/>
-      <c r="G104" s="39"/>
-      <c r="H104" s="38"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="36"/>
+      <c r="H104" s="35"/>
       <c r="I104" s="10"/>
     </row>
     <row r="105" spans="2:9">
-      <c r="B105" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C105" s="38"/>
-      <c r="D105" s="37" t="s">
+      <c r="B105" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C105" s="35"/>
+      <c r="D105" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="38"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="36"/>
+      <c r="H105" s="35"/>
       <c r="I105" s="10"/>
     </row>
     <row r="106" spans="2:9" s="1" customFormat="1">
@@ -5918,13 +5080,13 @@
       <c r="C107" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D107" s="34" t="s">
+      <c r="D107" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="E107" s="34"/>
-      <c r="F107" s="34"/>
-      <c r="G107" s="34"/>
-      <c r="H107" s="34"/>
+      <c r="E107" s="37"/>
+      <c r="F107" s="37"/>
+      <c r="G107" s="37"/>
+      <c r="H107" s="37"/>
       <c r="I107" s="9" t="s">
         <v>62</v>
       </c>
@@ -6008,31 +5170,31 @@
       </c>
     </row>
     <row r="114" spans="2:9">
-      <c r="B114" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C114" s="38"/>
-      <c r="D114" s="37" t="s">
+      <c r="B114" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C114" s="35"/>
+      <c r="D114" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E114" s="39"/>
-      <c r="F114" s="39"/>
-      <c r="G114" s="39"/>
-      <c r="H114" s="38"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="36"/>
+      <c r="G114" s="36"/>
+      <c r="H114" s="35"/>
       <c r="I114" s="10"/>
     </row>
     <row r="115" spans="2:9">
-      <c r="B115" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C115" s="38"/>
-      <c r="D115" s="37" t="s">
+      <c r="B115" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C115" s="35"/>
+      <c r="D115" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E115" s="39"/>
-      <c r="F115" s="39"/>
-      <c r="G115" s="39"/>
-      <c r="H115" s="38"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="36"/>
+      <c r="G115" s="36"/>
+      <c r="H115" s="35"/>
       <c r="I115" s="10"/>
     </row>
     <row r="116" spans="2:9" s="1" customFormat="1">
@@ -6068,13 +5230,13 @@
       <c r="C117" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D117" s="34" t="s">
+      <c r="D117" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="E117" s="34"/>
-      <c r="F117" s="34"/>
-      <c r="G117" s="34"/>
-      <c r="H117" s="34"/>
+      <c r="E117" s="37"/>
+      <c r="F117" s="37"/>
+      <c r="G117" s="37"/>
+      <c r="H117" s="37"/>
       <c r="I117" s="9" t="s">
         <v>69</v>
       </c>
@@ -6222,31 +5384,31 @@
       </c>
     </row>
     <row r="127" spans="2:9">
-      <c r="B127" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" s="38"/>
-      <c r="D127" s="37" t="s">
+      <c r="B127" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C127" s="35"/>
+      <c r="D127" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E127" s="39"/>
-      <c r="F127" s="39"/>
-      <c r="G127" s="39"/>
-      <c r="H127" s="38"/>
+      <c r="E127" s="36"/>
+      <c r="F127" s="36"/>
+      <c r="G127" s="36"/>
+      <c r="H127" s="35"/>
       <c r="I127" s="10"/>
     </row>
     <row r="128" spans="2:9">
-      <c r="B128" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C128" s="38"/>
-      <c r="D128" s="37" t="s">
+      <c r="B128" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C128" s="35"/>
+      <c r="D128" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E128" s="39"/>
-      <c r="F128" s="39"/>
-      <c r="G128" s="39"/>
-      <c r="H128" s="38"/>
+      <c r="E128" s="36"/>
+      <c r="F128" s="36"/>
+      <c r="G128" s="36"/>
+      <c r="H128" s="35"/>
       <c r="I128" s="10"/>
     </row>
     <row r="129" spans="2:9" s="1" customFormat="1">
@@ -6282,13 +5444,13 @@
       <c r="C130" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D130" s="34" t="s">
+      <c r="D130" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="E130" s="34"/>
-      <c r="F130" s="34"/>
-      <c r="G130" s="34"/>
-      <c r="H130" s="34"/>
+      <c r="E130" s="37"/>
+      <c r="F130" s="37"/>
+      <c r="G130" s="37"/>
+      <c r="H130" s="37"/>
       <c r="I130" s="9" t="s">
         <v>78</v>
       </c>
@@ -6372,31 +5534,31 @@
       </c>
     </row>
     <row r="137" spans="2:9">
-      <c r="B137" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C137" s="38"/>
-      <c r="D137" s="37" t="s">
+      <c r="B137" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C137" s="35"/>
+      <c r="D137" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E137" s="39"/>
-      <c r="F137" s="39"/>
-      <c r="G137" s="39"/>
-      <c r="H137" s="38"/>
+      <c r="E137" s="36"/>
+      <c r="F137" s="36"/>
+      <c r="G137" s="36"/>
+      <c r="H137" s="35"/>
       <c r="I137" s="10"/>
     </row>
     <row r="138" spans="2:9">
-      <c r="B138" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C138" s="38"/>
-      <c r="D138" s="37" t="s">
+      <c r="B138" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C138" s="35"/>
+      <c r="D138" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E138" s="39"/>
-      <c r="F138" s="39"/>
-      <c r="G138" s="39"/>
-      <c r="H138" s="38"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+      <c r="G138" s="36"/>
+      <c r="H138" s="35"/>
       <c r="I138" s="10"/>
     </row>
     <row r="139" spans="2:9" s="1" customFormat="1">
@@ -6432,13 +5594,13 @@
       <c r="C140" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D140" s="34" t="s">
+      <c r="D140" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="E140" s="34"/>
-      <c r="F140" s="34"/>
-      <c r="G140" s="34"/>
-      <c r="H140" s="34"/>
+      <c r="E140" s="37"/>
+      <c r="F140" s="37"/>
+      <c r="G140" s="37"/>
+      <c r="H140" s="37"/>
       <c r="I140" s="9" t="s">
         <v>83</v>
       </c>
@@ -6586,31 +5748,31 @@
       </c>
     </row>
     <row r="150" spans="2:9">
-      <c r="B150" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C150" s="38"/>
-      <c r="D150" s="37" t="s">
+      <c r="B150" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C150" s="35"/>
+      <c r="D150" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E150" s="39"/>
-      <c r="F150" s="39"/>
-      <c r="G150" s="39"/>
-      <c r="H150" s="38"/>
+      <c r="E150" s="36"/>
+      <c r="F150" s="36"/>
+      <c r="G150" s="36"/>
+      <c r="H150" s="35"/>
       <c r="I150" s="10"/>
     </row>
     <row r="151" spans="2:9">
-      <c r="B151" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C151" s="38"/>
-      <c r="D151" s="37" t="s">
+      <c r="B151" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C151" s="35"/>
+      <c r="D151" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E151" s="39"/>
-      <c r="F151" s="39"/>
-      <c r="G151" s="39"/>
-      <c r="H151" s="38"/>
+      <c r="E151" s="36"/>
+      <c r="F151" s="36"/>
+      <c r="G151" s="36"/>
+      <c r="H151" s="35"/>
       <c r="I151" s="10"/>
     </row>
     <row r="152" spans="2:9" s="1" customFormat="1">
@@ -6646,13 +5808,13 @@
       <c r="C153" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D153" s="34" t="s">
+      <c r="D153" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="E153" s="34"/>
-      <c r="F153" s="34"/>
-      <c r="G153" s="34"/>
-      <c r="H153" s="34"/>
+      <c r="E153" s="37"/>
+      <c r="F153" s="37"/>
+      <c r="G153" s="37"/>
+      <c r="H153" s="37"/>
       <c r="I153" s="9" t="s">
         <v>94</v>
       </c>
@@ -6879,7 +6041,7 @@
     </row>
     <row r="191" spans="11:15">
       <c r="L191" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="192" spans="11:15">
@@ -6920,10 +6082,10 @@
       <c r="E198" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F198" s="31" t="s">
+      <c r="F198" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="G198" s="32"/>
+      <c r="G198" s="40"/>
       <c r="K198" s="3" t="s">
         <v>413</v>
       </c>
@@ -6984,10 +6146,10 @@
       <c r="E205" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F205" s="31" t="s">
+      <c r="F205" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="G205" s="32"/>
+      <c r="G205" s="40"/>
       <c r="K205" s="3" t="s">
         <v>419</v>
       </c>
@@ -7034,15 +6196,15 @@
       <c r="E210" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F210" s="31" t="s">
+      <c r="F210" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="G210" s="32"/>
-      <c r="K210" s="42" t="s">
+      <c r="G210" s="40"/>
+      <c r="K210" s="28" t="s">
         <v>423</v>
       </c>
-      <c r="L210" s="43" t="s">
-        <v>482</v>
+      <c r="L210" s="29" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="5:12">
@@ -7053,11 +6215,11 @@
         <v>171</v>
       </c>
       <c r="G211" s="8"/>
-      <c r="K211" s="24" t="s">
+      <c r="K211" s="23" t="s">
         <v>424</v>
       </c>
-      <c r="L211" s="41" t="s">
-        <v>483</v>
+      <c r="L211" s="27" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="5:12">
@@ -7068,11 +6230,11 @@
         <v>172</v>
       </c>
       <c r="G212" s="8"/>
-      <c r="K212" s="24" t="s">
+      <c r="K212" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="L212" s="41" t="s">
-        <v>484</v>
+      <c r="L212" s="27" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="5:12">
@@ -7083,21 +6245,21 @@
         <v>173</v>
       </c>
       <c r="G213" s="8"/>
-      <c r="K213" s="24" t="s">
+      <c r="K213" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="L213" s="41" t="s">
-        <v>485</v>
+      <c r="L213" s="27" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="5:12">
       <c r="E215" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F215" s="31" t="s">
+      <c r="F215" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="G215" s="32"/>
+      <c r="G215" s="40"/>
       <c r="K215" s="3" t="s">
         <v>426</v>
       </c>
@@ -7142,11 +6304,11 @@
       </c>
     </row>
     <row r="219" spans="5:12">
-      <c r="K219" s="44" t="s">
+      <c r="K219" s="30" t="s">
         <v>428</v>
       </c>
-      <c r="L219" s="45" t="s">
-        <v>486</v>
+      <c r="L219" s="31" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="5:12">
@@ -7374,11 +6536,97 @@
     </row>
     <row r="245" spans="5:11">
       <c r="K245" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="F205:G205"/>
+    <mergeCell ref="F210:G210"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="D151:H151"/>
+    <mergeCell ref="D153:H153"/>
+    <mergeCell ref="D140:H140"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="D150:H150"/>
+    <mergeCell ref="D95:H95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:H96"/>
+    <mergeCell ref="D98:H98"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:H104"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:H74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="D77:H77"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="B4:C4"/>
@@ -7403,92 +6651,6 @@
     <mergeCell ref="B115:C115"/>
     <mergeCell ref="D115:H115"/>
     <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="D151:H151"/>
-    <mergeCell ref="D153:H153"/>
-    <mergeCell ref="D140:H140"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="D150:H150"/>
-    <mergeCell ref="D95:H95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:H96"/>
-    <mergeCell ref="D98:H98"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="D104:H104"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:H74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="D77:H77"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="F205:G205"/>
-    <mergeCell ref="F210:G210"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D41:H41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7499,162 +6661,168 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D372CB6-24DE-CF45-B52E-C0326906BAD2}">
-  <dimension ref="B2:B45"/>
+  <dimension ref="B2:B42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="16384" width="10.625" style="43"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:2" ht="23">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="42" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="23">
+      <c r="B3" s="42" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="23">
+      <c r="B4" s="42" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="23">
+      <c r="B7" s="42" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="23">
+      <c r="B8" s="42" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="23">
+      <c r="B9" s="42" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="23">
+      <c r="B10" s="42"/>
+    </row>
+    <row r="11" spans="2:2" ht="23">
+      <c r="B11" s="42" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="23">
+      <c r="B12" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="23">
+      <c r="B13" s="44" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="23">
+      <c r="B14" s="44" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" ht="23">
+      <c r="B15" s="44" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="23">
+      <c r="B16" s="44" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="23">
+      <c r="B20" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="23">
+      <c r="B21" s="44" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="23">
+      <c r="B22" s="44" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="23">
+      <c r="B23" s="44" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="23">
+      <c r="B24" s="44" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="23">
+      <c r="B27" s="42" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="23">
-      <c r="B3" s="23" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="23">
-      <c r="B4" s="23" t="s">
+    <row r="28" spans="2:2" ht="23">
+      <c r="B28" s="44" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="23">
-      <c r="B7" s="23" t="s">
+    <row r="29" spans="2:2" ht="23">
+      <c r="B29" s="44" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="23">
-      <c r="B8" s="23" t="s">
+    <row r="30" spans="2:2" ht="23">
+      <c r="B30" s="44" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="23">
-      <c r="B9" s="23" t="s">
+    <row r="31" spans="2:2" ht="23">
+      <c r="B31" s="44" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="23">
-      <c r="B14" s="23" t="s">
+    <row r="32" spans="2:2" ht="23">
+      <c r="B32" s="44" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" ht="23">
+      <c r="B33" s="44" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="23">
+      <c r="B34" s="42" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="23">
+      <c r="B35" s="42" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="23">
+      <c r="B36" s="44" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" ht="23">
+      <c r="B38" s="44" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="23">
+      <c r="B39" s="44" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="23">
-      <c r="B15" s="28" t="s">
+    <row r="40" spans="2:2" ht="23">
+      <c r="B40" s="44" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="23">
-      <c r="B16" s="28" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="23">
-      <c r="B17" s="28" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" ht="23">
-      <c r="B18" s="28" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="23">
-      <c r="B19" s="29" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" ht="23">
-      <c r="B23" s="23" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" ht="23">
-      <c r="B24" s="28" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" ht="23">
-      <c r="B25" s="28" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" ht="23">
-      <c r="B26" s="28" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" ht="23">
-      <c r="B27" s="29" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" ht="23">
-      <c r="B30" s="23" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" ht="23">
-      <c r="B31" s="28" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" ht="23">
-      <c r="B32" s="28" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="23">
-      <c r="B33" s="28" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="23">
-      <c r="B34" s="28" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="23">
-      <c r="B35" s="28" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="23">
-      <c r="B36" s="28" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" ht="23">
-      <c r="B37" s="23" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="23">
-      <c r="B38" s="23" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="23">
-      <c r="B39" s="29" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" ht="23">
-      <c r="B41" s="30" t="s">
-        <v>473</v>
-      </c>
-    </row>
     <row r="42" spans="2:2" ht="23">
-      <c r="B42" s="30" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="23">
-      <c r="B43" s="30" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" ht="23">
-      <c r="B45" s="23" t="s">
-        <v>476</v>
+      <c r="B42" s="42" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -7681,14 +6849,14 @@
     <col min="11" max="11" width="10" style="18"/>
     <col min="12" max="12" width="23" style="18" customWidth="1"/>
     <col min="13" max="13" width="21.5" style="19" customWidth="1"/>
-    <col min="14" max="14" width="15.375" style="27" customWidth="1"/>
+    <col min="14" max="14" width="15.375" style="26" customWidth="1"/>
     <col min="15" max="15" width="3.5" customWidth="1"/>
     <col min="16" max="16" width="1.75" style="18" customWidth="1"/>
     <col min="17" max="17" width="10" style="18"/>
     <col min="18" max="18" width="25.125" style="18" customWidth="1"/>
-    <col min="19" max="19" width="16.25" style="25" customWidth="1"/>
+    <col min="19" max="19" width="16.25" style="24" customWidth="1"/>
     <col min="20" max="20" width="21.5" style="19" customWidth="1"/>
-    <col min="21" max="21" width="26.625" style="27" customWidth="1"/>
+    <col min="21" max="21" width="26.625" style="26" customWidth="1"/>
     <col min="22" max="22" width="10.875" style="18" customWidth="1"/>
     <col min="23" max="23" width="8.125" style="21" customWidth="1"/>
     <col min="24" max="24" width="7.125" style="22" customWidth="1"/>
@@ -7716,7 +6884,7 @@
       <c r="M2" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="26" t="s">
         <v>131</v>
       </c>
       <c r="O2" s="18" t="s">
@@ -7728,11 +6896,11 @@
       <c r="T2" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="U2" s="26" t="s">
         <v>136</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="W2" s="21" t="s">
         <v>406</v>
@@ -7779,7 +6947,7 @@
       <c r="M4" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="N4" s="27" t="s">
+      <c r="N4" s="26" t="s">
         <v>288</v>
       </c>
       <c r="O4">
@@ -7791,13 +6959,13 @@
       <c r="R4" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S4" s="26" t="s">
-        <v>452</v>
+      <c r="S4" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T4" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="U4" s="26" t="s">
         <v>331</v>
       </c>
       <c r="V4" s="18">
@@ -7848,7 +7016,7 @@
       <c r="M5" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="N5" s="27" t="s">
+      <c r="N5" s="26" t="s">
         <v>290</v>
       </c>
       <c r="O5">
@@ -7860,13 +7028,13 @@
       <c r="R5" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S5" s="26" t="s">
-        <v>452</v>
+      <c r="S5" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T5" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="U5" s="27" t="s">
+      <c r="U5" s="26" t="s">
         <v>332</v>
       </c>
       <c r="V5" s="18">
@@ -7917,7 +7085,7 @@
       <c r="M6" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="N6" s="27" t="s">
+      <c r="N6" s="26" t="s">
         <v>291</v>
       </c>
       <c r="O6">
@@ -7929,13 +7097,13 @@
       <c r="R6" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S6" s="26" t="s">
-        <v>452</v>
+      <c r="S6" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T6" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="U6" s="27" t="s">
+      <c r="U6" s="26" t="s">
         <v>333</v>
       </c>
       <c r="V6" s="18">
@@ -7986,7 +7154,7 @@
       <c r="M7" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="N7" s="27" t="s">
+      <c r="N7" s="26" t="s">
         <v>294</v>
       </c>
       <c r="O7">
@@ -7998,13 +7166,13 @@
       <c r="R7" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S7" s="26" t="s">
-        <v>452</v>
+      <c r="S7" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T7" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="U7" s="27" t="s">
+      <c r="U7" s="26" t="s">
         <v>334</v>
       </c>
       <c r="V7" s="18">
@@ -8055,7 +7223,7 @@
       <c r="M8" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="N8" s="27" t="s">
+      <c r="N8" s="26" t="s">
         <v>296</v>
       </c>
       <c r="O8">
@@ -8067,13 +7235,13 @@
       <c r="R8" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S8" s="26" t="s">
-        <v>452</v>
+      <c r="S8" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T8" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="U8" s="27" t="s">
+      <c r="U8" s="26" t="s">
         <v>335</v>
       </c>
       <c r="V8" s="18">
@@ -8124,7 +7292,7 @@
       <c r="M9" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="N9" s="27" t="s">
+      <c r="N9" s="26" t="s">
         <v>298</v>
       </c>
       <c r="O9">
@@ -8136,13 +7304,13 @@
       <c r="R9" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S9" s="26" t="s">
-        <v>452</v>
+      <c r="S9" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T9" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="U9" s="27" t="s">
+      <c r="U9" s="26" t="s">
         <v>336</v>
       </c>
       <c r="V9" s="18">
@@ -8193,7 +7361,7 @@
       <c r="M10" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="N10" s="27" t="s">
+      <c r="N10" s="26" t="s">
         <v>300</v>
       </c>
       <c r="O10">
@@ -8205,13 +7373,13 @@
       <c r="R10" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S10" s="26" t="s">
-        <v>452</v>
+      <c r="S10" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T10" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="U10" s="27" t="s">
+      <c r="U10" s="26" t="s">
         <v>337</v>
       </c>
       <c r="V10" s="18">
@@ -8262,7 +7430,7 @@
       <c r="M11" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="N11" s="27" t="s">
+      <c r="N11" s="26" t="s">
         <v>302</v>
       </c>
       <c r="O11">
@@ -8274,13 +7442,13 @@
       <c r="R11" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S11" s="26" t="s">
-        <v>452</v>
+      <c r="S11" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T11" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="U11" s="27" t="s">
+      <c r="U11" s="26" t="s">
         <v>338</v>
       </c>
       <c r="V11" s="18">
@@ -8331,7 +7499,7 @@
       <c r="M12" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="N12" s="27" t="s">
+      <c r="N12" s="26" t="s">
         <v>304</v>
       </c>
       <c r="O12">
@@ -8343,13 +7511,13 @@
       <c r="R12" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S12" s="26" t="s">
-        <v>452</v>
+      <c r="S12" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T12" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="U12" s="27" t="s">
+      <c r="U12" s="26" t="s">
         <v>339</v>
       </c>
       <c r="V12" s="18">
@@ -8400,7 +7568,7 @@
       <c r="M13" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="N13" s="27" t="s">
+      <c r="N13" s="26" t="s">
         <v>306</v>
       </c>
       <c r="O13">
@@ -8412,13 +7580,13 @@
       <c r="R13" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S13" s="26" t="s">
-        <v>452</v>
+      <c r="S13" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T13" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="U13" s="27" t="s">
+      <c r="U13" s="26" t="s">
         <v>340</v>
       </c>
       <c r="V13" s="18">
@@ -8469,7 +7637,7 @@
       <c r="M14" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="N14" s="27" t="s">
+      <c r="N14" s="26" t="s">
         <v>308</v>
       </c>
       <c r="O14">
@@ -8481,13 +7649,13 @@
       <c r="R14" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S14" s="26" t="s">
-        <v>452</v>
+      <c r="S14" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T14" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="U14" s="27" t="s">
+      <c r="U14" s="26" t="s">
         <v>341</v>
       </c>
       <c r="V14" s="18">
@@ -8538,7 +7706,7 @@
       <c r="M15" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="N15" s="27" t="s">
+      <c r="N15" s="26" t="s">
         <v>310</v>
       </c>
       <c r="O15">
@@ -8550,13 +7718,13 @@
       <c r="R15" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S15" s="26" t="s">
-        <v>452</v>
+      <c r="S15" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T15" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="U15" s="27" t="s">
+      <c r="U15" s="26" t="s">
         <v>342</v>
       </c>
       <c r="V15" s="18">
@@ -8607,7 +7775,7 @@
       <c r="M16" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="N16" s="27" t="s">
+      <c r="N16" s="26" t="s">
         <v>312</v>
       </c>
       <c r="O16">
@@ -8619,13 +7787,13 @@
       <c r="R16" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S16" s="26" t="s">
-        <v>452</v>
+      <c r="S16" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T16" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="U16" s="27" t="s">
+      <c r="U16" s="26" t="s">
         <v>343</v>
       </c>
       <c r="V16" s="18">
@@ -8676,7 +7844,7 @@
       <c r="M17" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="N17" s="27" t="s">
+      <c r="N17" s="26" t="s">
         <v>314</v>
       </c>
       <c r="O17">
@@ -8688,13 +7856,13 @@
       <c r="R17" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S17" s="26" t="s">
-        <v>452</v>
+      <c r="S17" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T17" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="U17" s="27" t="s">
+      <c r="U17" s="26" t="s">
         <v>344</v>
       </c>
       <c r="V17" s="18">
@@ -8745,7 +7913,7 @@
       <c r="M18" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="N18" s="27" t="s">
+      <c r="N18" s="26" t="s">
         <v>316</v>
       </c>
       <c r="O18">
@@ -8757,13 +7925,13 @@
       <c r="R18" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S18" s="26" t="s">
-        <v>452</v>
+      <c r="S18" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T18" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="U18" s="27" t="s">
+      <c r="U18" s="26" t="s">
         <v>345</v>
       </c>
       <c r="V18" s="18">
@@ -8814,7 +7982,7 @@
       <c r="M19" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="N19" s="27" t="s">
+      <c r="N19" s="26" t="s">
         <v>318</v>
       </c>
       <c r="O19">
@@ -8826,13 +7994,13 @@
       <c r="R19" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S19" s="26" t="s">
-        <v>452</v>
+      <c r="S19" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T19" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="U19" s="27" t="s">
+      <c r="U19" s="26" t="s">
         <v>346</v>
       </c>
       <c r="V19" s="18">
@@ -8883,7 +8051,7 @@
       <c r="M20" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="N20" s="27" t="s">
+      <c r="N20" s="26" t="s">
         <v>319</v>
       </c>
       <c r="O20">
@@ -8895,13 +8063,13 @@
       <c r="R20" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S20" s="26" t="s">
-        <v>452</v>
+      <c r="S20" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T20" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="U20" s="27" t="s">
+      <c r="U20" s="26" t="s">
         <v>347</v>
       </c>
       <c r="V20" s="18">
@@ -8952,7 +8120,7 @@
       <c r="M21" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="N21" s="27" t="s">
+      <c r="N21" s="26" t="s">
         <v>322</v>
       </c>
       <c r="O21">
@@ -8964,13 +8132,13 @@
       <c r="R21" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S21" s="26" t="s">
-        <v>452</v>
+      <c r="S21" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T21" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="U21" s="27" t="s">
+      <c r="U21" s="26" t="s">
         <v>348</v>
       </c>
       <c r="V21" s="18">
@@ -9021,7 +8189,7 @@
       <c r="M22" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="N22" s="27" t="s">
+      <c r="N22" s="26" t="s">
         <v>324</v>
       </c>
       <c r="O22">
@@ -9033,13 +8201,13 @@
       <c r="R22" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S22" s="26" t="s">
-        <v>452</v>
+      <c r="S22" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T22" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="U22" s="27" t="s">
+      <c r="U22" s="26" t="s">
         <v>349</v>
       </c>
       <c r="V22" s="18">
@@ -9090,7 +8258,7 @@
       <c r="M23" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="N23" s="27" t="s">
+      <c r="N23" s="26" t="s">
         <v>326</v>
       </c>
       <c r="O23">
@@ -9102,13 +8270,13 @@
       <c r="R23" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S23" s="26" t="s">
-        <v>452</v>
+      <c r="S23" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T23" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="U23" s="27" t="s">
+      <c r="U23" s="26" t="s">
         <v>350</v>
       </c>
       <c r="V23" s="18">
@@ -9159,7 +8327,7 @@
       <c r="M24" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="N24" s="27" t="s">
+      <c r="N24" s="26" t="s">
         <v>316</v>
       </c>
       <c r="O24">
@@ -9171,13 +8339,13 @@
       <c r="R24" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S24" s="26" t="s">
-        <v>452</v>
+      <c r="S24" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T24" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="U24" s="27" t="s">
+      <c r="U24" s="26" t="s">
         <v>351</v>
       </c>
       <c r="V24" s="18">
@@ -9228,7 +8396,7 @@
       <c r="M25" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="N25" s="27" t="s">
+      <c r="N25" s="26" t="s">
         <v>329</v>
       </c>
       <c r="O25">
@@ -9240,13 +8408,13 @@
       <c r="R25" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S25" s="26" t="s">
-        <v>452</v>
+      <c r="S25" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T25" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="U25" s="27" t="s">
+      <c r="U25" s="26" t="s">
         <v>352</v>
       </c>
       <c r="V25" s="18">
@@ -9294,13 +8462,13 @@
       <c r="R26" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S26" s="26" t="s">
-        <v>452</v>
+      <c r="S26" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T26" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="U26" s="27" t="s">
+      <c r="U26" s="26" t="s">
         <v>353</v>
       </c>
       <c r="V26" s="18">
@@ -9348,13 +8516,13 @@
       <c r="R27" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S27" s="26" t="s">
-        <v>452</v>
+      <c r="S27" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T27" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="U27" s="27" t="s">
+      <c r="U27" s="26" t="s">
         <v>354</v>
       </c>
       <c r="V27" s="18">
@@ -9402,13 +8570,13 @@
       <c r="R28" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S28" s="26" t="s">
-        <v>452</v>
+      <c r="S28" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T28" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="U28" s="27" t="s">
+      <c r="U28" s="26" t="s">
         <v>355</v>
       </c>
       <c r="V28" s="18">
@@ -9456,13 +8624,13 @@
       <c r="R29" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S29" s="26" t="s">
-        <v>452</v>
+      <c r="S29" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T29" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="U29" s="27" t="s">
+      <c r="U29" s="26" t="s">
         <v>356</v>
       </c>
       <c r="V29" s="18">
@@ -9510,13 +8678,13 @@
       <c r="R30" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S30" s="26" t="s">
-        <v>452</v>
+      <c r="S30" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T30" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="U30" s="27" t="s">
+      <c r="U30" s="26" t="s">
         <v>357</v>
       </c>
       <c r="V30" s="18">
@@ -9564,13 +8732,13 @@
       <c r="R31" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S31" s="26" t="s">
-        <v>452</v>
+      <c r="S31" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T31" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="U31" s="27" t="s">
+      <c r="U31" s="26" t="s">
         <v>358</v>
       </c>
       <c r="V31" s="18">
@@ -9618,13 +8786,13 @@
       <c r="R32" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S32" s="26" t="s">
-        <v>452</v>
+      <c r="S32" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T32" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="U32" s="27" t="s">
+      <c r="U32" s="26" t="s">
         <v>359</v>
       </c>
       <c r="V32" s="18">
@@ -9672,13 +8840,13 @@
       <c r="R33" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S33" s="26" t="s">
-        <v>452</v>
+      <c r="S33" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T33" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="U33" s="27" t="s">
+      <c r="U33" s="26" t="s">
         <v>360</v>
       </c>
       <c r="V33" s="18">
@@ -9726,13 +8894,13 @@
       <c r="R34" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S34" s="26" t="s">
-        <v>452</v>
+      <c r="S34" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T34" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="U34" s="27" t="s">
+      <c r="U34" s="26" t="s">
         <v>361</v>
       </c>
       <c r="V34" s="18">
@@ -9780,13 +8948,13 @@
       <c r="R35" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S35" s="26" t="s">
-        <v>452</v>
+      <c r="S35" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T35" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="U35" s="27" t="s">
+      <c r="U35" s="26" t="s">
         <v>362</v>
       </c>
       <c r="V35" s="18">
@@ -9807,13 +8975,13 @@
       <c r="R36" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S36" s="26" t="s">
-        <v>452</v>
+      <c r="S36" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T36" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="U36" s="27" t="s">
+      <c r="U36" s="26" t="s">
         <v>363</v>
       </c>
       <c r="V36" s="18">
@@ -9830,16 +8998,43 @@
       </c>
     </row>
     <row r="37" spans="2:30">
+      <c r="B37" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>487</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" s="46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F37" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="46" t="s">
+        <v>489</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I37" s="45">
+        <v>0</v>
+      </c>
+      <c r="J37" s="45" t="s">
+        <v>187</v>
+      </c>
       <c r="R37" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S37" s="26" t="s">
-        <v>452</v>
+      <c r="S37" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T37" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="U37" s="27" t="s">
+      <c r="U37" s="26" t="s">
         <v>364</v>
       </c>
       <c r="V37" s="18">
@@ -9859,13 +9054,13 @@
       <c r="R38" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S38" s="26" t="s">
-        <v>452</v>
+      <c r="S38" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T38" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="U38" s="27" t="s">
+      <c r="U38" s="26" t="s">
         <v>365</v>
       </c>
       <c r="V38" s="18">
@@ -9885,13 +9080,13 @@
       <c r="R39" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S39" s="26" t="s">
-        <v>452</v>
+      <c r="S39" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T39" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="U39" s="27" t="s">
+      <c r="U39" s="26" t="s">
         <v>366</v>
       </c>
       <c r="V39" s="18">
@@ -9911,13 +9106,13 @@
       <c r="R40" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S40" s="26" t="s">
-        <v>452</v>
+      <c r="S40" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T40" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="U40" s="27" t="s">
+      <c r="U40" s="26" t="s">
         <v>367</v>
       </c>
       <c r="V40" s="18">
@@ -9937,13 +9132,13 @@
       <c r="R41" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S41" s="26" t="s">
-        <v>452</v>
+      <c r="S41" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T41" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="U41" s="27" t="s">
+      <c r="U41" s="26" t="s">
         <v>368</v>
       </c>
       <c r="V41" s="18">
@@ -9963,13 +9158,13 @@
       <c r="R42" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S42" s="26" t="s">
-        <v>452</v>
+      <c r="S42" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T42" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="U42" s="27" t="s">
+      <c r="U42" s="26" t="s">
         <v>369</v>
       </c>
       <c r="V42" s="18">
@@ -9989,13 +9184,13 @@
       <c r="R43" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S43" s="26" t="s">
-        <v>452</v>
+      <c r="S43" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T43" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="U43" s="27" t="s">
+      <c r="U43" s="26" t="s">
         <v>370</v>
       </c>
       <c r="V43" s="18">
@@ -10015,13 +9210,13 @@
       <c r="R44" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S44" s="26" t="s">
-        <v>452</v>
+      <c r="S44" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T44" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="U44" s="27" t="s">
+      <c r="U44" s="26" t="s">
         <v>371</v>
       </c>
       <c r="V44" s="18">
@@ -10041,13 +9236,13 @@
       <c r="R45" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S45" s="26" t="s">
-        <v>452</v>
+      <c r="S45" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T45" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="U45" s="27" t="s">
+      <c r="U45" s="26" t="s">
         <v>372</v>
       </c>
       <c r="V45" s="18">
@@ -10067,13 +9262,13 @@
       <c r="R46" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S46" s="26" t="s">
-        <v>452</v>
+      <c r="S46" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T46" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="U46" s="27" t="s">
+      <c r="U46" s="26" t="s">
         <v>373</v>
       </c>
       <c r="V46" s="18">
@@ -10093,13 +9288,13 @@
       <c r="R47" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S47" s="26" t="s">
-        <v>452</v>
+      <c r="S47" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T47" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="U47" s="27" t="s">
+      <c r="U47" s="26" t="s">
         <v>374</v>
       </c>
       <c r="V47" s="18">
@@ -10119,13 +9314,13 @@
       <c r="R48" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S48" s="26" t="s">
-        <v>452</v>
+      <c r="S48" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T48" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="U48" s="27" t="s">
+      <c r="U48" s="26" t="s">
         <v>375</v>
       </c>
       <c r="V48" s="18">
@@ -10145,13 +9340,13 @@
       <c r="R49" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S49" s="26" t="s">
-        <v>452</v>
+      <c r="S49" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T49" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="U49" s="27" t="s">
+      <c r="U49" s="26" t="s">
         <v>376</v>
       </c>
       <c r="V49" s="18">
@@ -10171,13 +9366,13 @@
       <c r="R50" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S50" s="26" t="s">
-        <v>452</v>
+      <c r="S50" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T50" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="U50" s="27" t="s">
+      <c r="U50" s="26" t="s">
         <v>377</v>
       </c>
       <c r="V50" s="18">
@@ -10197,13 +9392,13 @@
       <c r="R51" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S51" s="26" t="s">
-        <v>452</v>
+      <c r="S51" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T51" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="U51" s="27" t="s">
+      <c r="U51" s="26" t="s">
         <v>378</v>
       </c>
       <c r="V51" s="18">
@@ -10223,13 +9418,13 @@
       <c r="R52" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S52" s="26" t="s">
-        <v>452</v>
+      <c r="S52" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T52" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="U52" s="27" t="s">
+      <c r="U52" s="26" t="s">
         <v>379</v>
       </c>
       <c r="V52" s="18">
@@ -10249,13 +9444,13 @@
       <c r="R53" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S53" s="26" t="s">
-        <v>452</v>
+      <c r="S53" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T53" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="U53" s="27" t="s">
+      <c r="U53" s="26" t="s">
         <v>380</v>
       </c>
       <c r="V53" s="18">
@@ -10275,13 +9470,13 @@
       <c r="R54" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S54" s="26" t="s">
-        <v>452</v>
+      <c r="S54" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T54" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="U54" s="27" t="s">
+      <c r="U54" s="26" t="s">
         <v>381</v>
       </c>
       <c r="V54" s="18">
@@ -10301,13 +9496,13 @@
       <c r="R55" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S55" s="26" t="s">
-        <v>452</v>
+      <c r="S55" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T55" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="U55" s="27" t="s">
+      <c r="U55" s="26" t="s">
         <v>382</v>
       </c>
       <c r="V55" s="18">
@@ -10327,13 +9522,13 @@
       <c r="R56" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S56" s="26" t="s">
-        <v>452</v>
+      <c r="S56" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T56" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="U56" s="27" t="s">
+      <c r="U56" s="26" t="s">
         <v>383</v>
       </c>
       <c r="V56" s="18">
@@ -10353,13 +9548,13 @@
       <c r="R57" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S57" s="26" t="s">
-        <v>452</v>
+      <c r="S57" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T57" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="U57" s="27" t="s">
+      <c r="U57" s="26" t="s">
         <v>384</v>
       </c>
       <c r="V57" s="18">
@@ -10379,13 +9574,13 @@
       <c r="R58" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S58" s="26" t="s">
-        <v>452</v>
+      <c r="S58" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T58" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="U58" s="27" t="s">
+      <c r="U58" s="26" t="s">
         <v>385</v>
       </c>
       <c r="V58" s="18">
@@ -10405,13 +9600,13 @@
       <c r="R59" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S59" s="26" t="s">
-        <v>452</v>
+      <c r="S59" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T59" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="U59" s="27" t="s">
+      <c r="U59" s="26" t="s">
         <v>386</v>
       </c>
       <c r="V59" s="18">
@@ -10431,13 +9626,13 @@
       <c r="R60" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S60" s="26" t="s">
-        <v>452</v>
+      <c r="S60" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T60" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="U60" s="27" t="s">
+      <c r="U60" s="26" t="s">
         <v>387</v>
       </c>
       <c r="V60" s="18">
@@ -10457,13 +9652,13 @@
       <c r="R61" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S61" s="26" t="s">
-        <v>452</v>
+      <c r="S61" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T61" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="U61" s="27" t="s">
+      <c r="U61" s="26" t="s">
         <v>388</v>
       </c>
       <c r="V61" s="18">
@@ -10483,13 +9678,13 @@
       <c r="R62" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S62" s="26" t="s">
-        <v>452</v>
+      <c r="S62" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T62" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="U62" s="27" t="s">
+      <c r="U62" s="26" t="s">
         <v>389</v>
       </c>
       <c r="V62" s="18">
@@ -10509,13 +9704,13 @@
       <c r="R63" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S63" s="26" t="s">
-        <v>452</v>
+      <c r="S63" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T63" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="U63" s="27" t="s">
+      <c r="U63" s="26" t="s">
         <v>390</v>
       </c>
       <c r="V63" s="18">
@@ -10535,13 +9730,13 @@
       <c r="R64" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S64" s="26" t="s">
-        <v>452</v>
+      <c r="S64" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T64" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="U64" s="27" t="s">
+      <c r="U64" s="26" t="s">
         <v>391</v>
       </c>
       <c r="V64" s="18">
@@ -10561,13 +9756,13 @@
       <c r="R65" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S65" s="26" t="s">
-        <v>452</v>
+      <c r="S65" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T65" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="U65" s="27" t="s">
+      <c r="U65" s="26" t="s">
         <v>392</v>
       </c>
       <c r="V65" s="18">
@@ -10587,13 +9782,13 @@
       <c r="R66" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S66" s="26" t="s">
-        <v>452</v>
+      <c r="S66" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T66" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="U66" s="27" t="s">
+      <c r="U66" s="26" t="s">
         <v>393</v>
       </c>
       <c r="V66" s="18">
@@ -10613,13 +9808,13 @@
       <c r="R67" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S67" s="26" t="s">
-        <v>452</v>
+      <c r="S67" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T67" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="U67" s="27" t="s">
+      <c r="U67" s="26" t="s">
         <v>394</v>
       </c>
       <c r="V67" s="18">
@@ -10639,13 +9834,13 @@
       <c r="R68" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S68" s="26" t="s">
-        <v>452</v>
+      <c r="S68" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T68" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="U68" s="27" t="s">
+      <c r="U68" s="26" t="s">
         <v>395</v>
       </c>
       <c r="V68" s="18">
@@ -10665,13 +9860,13 @@
       <c r="R69" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S69" s="26" t="s">
-        <v>452</v>
+      <c r="S69" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T69" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="U69" s="27" t="s">
+      <c r="U69" s="26" t="s">
         <v>396</v>
       </c>
       <c r="V69" s="18">
@@ -10691,13 +9886,13 @@
       <c r="R70" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S70" s="26" t="s">
-        <v>452</v>
+      <c r="S70" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T70" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="U70" s="27" t="s">
+      <c r="U70" s="26" t="s">
         <v>397</v>
       </c>
       <c r="V70" s="18">
@@ -10717,13 +9912,13 @@
       <c r="R71" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S71" s="26" t="s">
-        <v>452</v>
+      <c r="S71" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T71" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="U71" s="27" t="s">
+      <c r="U71" s="26" t="s">
         <v>398</v>
       </c>
       <c r="V71" s="18">
@@ -10743,13 +9938,13 @@
       <c r="R72" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S72" s="26" t="s">
-        <v>452</v>
+      <c r="S72" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T72" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="U72" s="27" t="s">
+      <c r="U72" s="26" t="s">
         <v>399</v>
       </c>
       <c r="V72" s="18">
@@ -10769,13 +9964,13 @@
       <c r="R73" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S73" s="26" t="s">
-        <v>452</v>
+      <c r="S73" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T73" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="U73" s="27" t="s">
+      <c r="U73" s="26" t="s">
         <v>400</v>
       </c>
       <c r="V73" s="18">
@@ -10795,13 +9990,13 @@
       <c r="R74" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S74" s="26" t="s">
-        <v>452</v>
+      <c r="S74" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T74" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="U74" s="27" t="s">
+      <c r="U74" s="26" t="s">
         <v>401</v>
       </c>
       <c r="V74" s="18">
@@ -10821,13 +10016,13 @@
       <c r="R75" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S75" s="26" t="s">
-        <v>452</v>
+      <c r="S75" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T75" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="U75" s="27" t="s">
+      <c r="U75" s="26" t="s">
         <v>402</v>
       </c>
       <c r="V75" s="18">
@@ -10847,13 +10042,13 @@
       <c r="R76" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S76" s="26" t="s">
-        <v>452</v>
+      <c r="S76" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T76" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="U76" s="27" t="s">
+      <c r="U76" s="26" t="s">
         <v>403</v>
       </c>
       <c r="V76" s="18">
@@ -10873,13 +10068,13 @@
       <c r="R77" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S77" s="26" t="s">
-        <v>452</v>
+      <c r="S77" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T77" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="U77" s="27" t="s">
+      <c r="U77" s="26" t="s">
         <v>404</v>
       </c>
       <c r="V77" s="18">
@@ -10899,13 +10094,13 @@
       <c r="R78" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="S78" s="26" t="s">
-        <v>452</v>
+      <c r="S78" s="25" t="s">
+        <v>451</v>
       </c>
       <c r="T78" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="U78" s="27" t="s">
+      <c r="U78" s="26" t="s">
         <v>405</v>
       </c>
       <c r="V78" s="18">

--- a/Human-JAVA/Human_11m_project/1108JavaTASK.xlsx
+++ b/Human-JAVA/Human_11m_project/1108JavaTASK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuuri/Study/Human-JAVA/Human_11m_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7363B130-AEE3-4744-A47D-63C8F7A47922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A119FC07-1CEE-8A4A-A21A-2002FE2244BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="2" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,47 +37,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={DD2A3BE1-3C96-E04B-A3D0-8D1B798C81FA}</author>
-    <author>tc={1EA2E108-1C7D-AA40-99D7-BFEC7B18B855}</author>
-    <author>tc={83CA8402-4DB7-DD41-9C58-B44DB8805882}</author>
-  </authors>
-  <commentList>
-    <comment ref="K210" authorId="0" shapeId="0" xr:uid="{DD2A3BE1-3C96-E04B-A3D0-8D1B798C81FA}">
-      <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    SELECT * FROM Book;SELECT * FROM Book;</t>
-      </text>
-    </comment>
-    <comment ref="K211" authorId="1" shapeId="0" xr:uid="{1EA2E108-1C7D-AA40-99D7-BFEC7B18B855}">
-      <text>
-        <t xml:space="preserve">[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    SELECT rnum AS Review_Number , book AS TITLE , rtext AS Review , rec AS Recommend , M.name AS NAME
-FROM Review R, Members M 
-WHERE R.id = M.id AND R.book LIKE '%검색 키워드%';
-</t>
-      </text>
-    </comment>
-    <comment ref="K219" authorId="2" shapeId="0" xr:uid="{83CA8402-4DB7-DD41-9C58-B44DB8805882}">
-      <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    SELECT name , id , point FROM Members WHERE name = '유저이름';</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="498">
   <si>
     <t>패키지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1542,10 +1503,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2. 시작 화면에선 3가지 메뉴가 나온다(로그인/회원가입/비회원전용)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로그인 화면 시나리오</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1723,10 +1680,6 @@
     <t>*/</t>
   </si>
   <si>
-    <t xml:space="preserve"> -&gt;  SELECT * FROM Book;SELECT * FROM Book;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SELECT rnum AS Review_Number , book AS TITLE , rtext AS Review , rec AS Recommend , M.name AS NAME</t>
   </si>
   <si>
@@ -1734,11 +1687,1298 @@
   </si>
   <si>
     <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">id </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(10) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pw </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10) ,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">name </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">point </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(10) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">book </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(30) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">author </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rec </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(3) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>create</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rnum </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(30) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">book </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(30),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rtext </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(500),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rec </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(1) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>CHECK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (rec </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>IN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(0, 1));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">id </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>varchar2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">wdate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>timestamp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>sysdate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>foreign</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (book) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Book(book) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>cascade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>foreign</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>references</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Members(id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>set</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>null</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>SEQUENCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> Review_no </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>INCREMENT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="D2Coding ligature"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 1;</t>
+    </r>
+  </si>
+  <si>
+    <t>admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>human</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 시작 화면에선 3가지 메뉴가 나온다(로그인/회원가입/비회원전용/관리자전용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자 전용 화면 시나리오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 아이디와 패스워드를 입력받는다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. DB에 id : admin , pw : human 이 일치된 정보를 검색해서 rs로 가져온다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT * FROM Book;SELECT * FROM Book;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT id, pw, name</t>
+  </si>
+  <si>
+    <t>FROM members</t>
+  </si>
+  <si>
+    <t>WHERE id = 'admin' AND pw = 'human';</t>
+  </si>
+  <si>
+    <r>
       <t>WHERE R.id = M.id AND R.book LIKE '%</t>
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="15"/>
         <color rgb="FF000000"/>
         <rFont val="Apple SD Gothic Neo"/>
         <family val="2"/>
@@ -1748,7 +2988,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="15"/>
         <color rgb="FF000000"/>
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
@@ -1757,7 +2997,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="15"/>
         <color rgb="FF000000"/>
         <rFont val="Apple SD Gothic Neo"/>
         <family val="2"/>
@@ -1767,7 +3007,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="15"/>
         <color rgb="FF000000"/>
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
@@ -1781,7 +3021,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="15"/>
         <color rgb="FF000000"/>
         <rFont val="Apple SD Gothic Neo"/>
         <family val="2"/>
@@ -1791,7 +3031,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="13"/>
+        <sz val="15"/>
         <color rgb="FF000000"/>
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
@@ -1800,1261 +3040,11 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Members;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Book;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Review;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DROP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Review;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DROP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Book;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DROP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Members;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CREATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Members(</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">id </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(10) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>PRIMARY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>KEY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">pw </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(10) ,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">name </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(10),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">point </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(10) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 0</t>
-    </r>
-  </si>
-  <si>
-    <t>);</t>
-  </si>
-  <si>
-    <r>
-      <t>CREATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Book(</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">book </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(30) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>PRIMARY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>KEY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">author </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(10),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">rec </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(3) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>create</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>table</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Review(</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">rnum </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(30) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>primary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">book </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(30),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">rtext </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(500),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">rec </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>number</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(1) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>CHECK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> (rec </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>IN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(0, 1));</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">id </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>varchar2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(10),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">wdate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>timestamp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>sysdate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>foreign</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> (book) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>REFERENCES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Book(book) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>cascade</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>foreign</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> (id) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>references</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Members(id) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>set</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>null</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CREATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>SEQUENCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> Review_no </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>INCREMENT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>BY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="D2Coding ligature"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 1;</t>
-    </r>
-  </si>
-  <si>
-    <t>admin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>human</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자</t>
+    <t>3. 입력된 아이디와 패스워드가 동일하다면 관리자 메뉴로 진입한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 관리자 메뉴 기능 (1. 책 등록, 2. 리뷰 삭제)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3069,7 +3059,7 @@
     <numFmt numFmtId="179" formatCode="@\,"/>
     <numFmt numFmtId="180" formatCode="\,\'@\'\,"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -3138,19 +3128,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Apple SD Gothic Neo"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
@@ -3162,6 +3139,34 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="D2Coding ligature"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="D2Coding ligature"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Apple SD Gothic Neo"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -3285,7 +3290,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3367,19 +3372,10 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3412,13 +3408,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3429,6 +3425,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3448,9 +3465,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="김가율" id="{02AF39A3-C54A-854D-8CA9-56AF642B00E4}" userId="S::2020610136@member.sdu.ac.kr::87b37c89-37d1-4042-9f07-aaed1eb32d02" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3748,26 +3763,9 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K210" dT="2023-11-08T13:26:54.69" personId="{02AF39A3-C54A-854D-8CA9-56AF642B00E4}" id="{DD2A3BE1-3C96-E04B-A3D0-8D1B798C81FA}">
-    <text>SELECT * FROM Book;SELECT * FROM Book;</text>
-  </threadedComment>
-  <threadedComment ref="K211" dT="2023-11-08T13:26:31.15" personId="{02AF39A3-C54A-854D-8CA9-56AF642B00E4}" id="{1EA2E108-1C7D-AA40-99D7-BFEC7B18B855}">
-    <text xml:space="preserve">SELECT rnum AS Review_Number , book AS TITLE , rtext AS Review , rec AS Recommend , M.name AS NAME
-FROM Review R, Members M 
-WHERE R.id = M.id AND R.book LIKE '%검색 키워드%';
-</text>
-  </threadedComment>
-  <threadedComment ref="K219" dT="2023-11-08T13:30:16.46" personId="{02AF39A3-C54A-854D-8CA9-56AF642B00E4}" id="{83CA8402-4DB7-DD41-9C58-B44DB8805882}">
-    <text>SELECT name , id , point FROM Members WHERE name = '유저이름';</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D20C97-A238-B548-AB04-E93343455A46}">
-  <dimension ref="A2:O245"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D20C97-A238-B548-AB04-E93343455A46}">
+  <dimension ref="A2:O248"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="23"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1"/>
@@ -3781,374 +3779,375 @@
     <col min="9" max="9" width="56" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.625" style="3"/>
     <col min="11" max="11" width="89.625" style="3" customWidth="1"/>
-    <col min="12" max="14" width="67.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="67.75" style="46" customWidth="1"/>
+    <col min="13" max="14" width="67.75" style="3" customWidth="1"/>
     <col min="15" max="15" width="62" style="3" customWidth="1"/>
     <col min="16" max="16384" width="10.625" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="37">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
       <c r="I3" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33" t="s">
+      <c r="C4" s="30"/>
+      <c r="D4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="33"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H5" s="33"/>
+      <c r="H5" s="30"/>
       <c r="I5" s="16" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33" t="s">
+      <c r="C6" s="30"/>
+      <c r="D6" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="33"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
       <c r="I6" s="16" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="30"/>
+      <c r="D7" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="33"/>
+      <c r="E7" s="30"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
       <c r="I7" s="16" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33" t="s">
+      <c r="C8" s="30"/>
+      <c r="D8" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="33"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="33"/>
+      <c r="H8" s="30"/>
       <c r="I8" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="16"/>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32" t="s">
+      <c r="C11" s="29"/>
+      <c r="D11" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
       <c r="I11" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33" t="s">
+      <c r="C12" s="30"/>
+      <c r="D12" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="33"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="33" t="s">
+      <c r="G12" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="33"/>
+      <c r="H12" s="30"/>
       <c r="I12" s="16"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="E13" s="33"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="30"/>
       <c r="I13" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33" t="s">
+      <c r="C14" s="30"/>
+      <c r="D14" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E14" s="33"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
       <c r="I14" s="16" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="16"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32" t="s">
+      <c r="C17" s="29"/>
+      <c r="D17" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33" t="s">
+      <c r="C18" s="30"/>
+      <c r="D18" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="33"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="33"/>
+      <c r="H18" s="30"/>
       <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33" t="s">
+      <c r="C19" s="30"/>
+      <c r="D19" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="33"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="16"/>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H19" s="33"/>
+      <c r="H19" s="30"/>
       <c r="I19" s="16" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33" t="s">
+      <c r="C20" s="30"/>
+      <c r="D20" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="33"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="33"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33" t="s">
+      <c r="C21" s="30"/>
+      <c r="D21" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="E21" s="33"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="16"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33" t="s">
+      <c r="C22" s="30"/>
+      <c r="D22" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="33"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="16"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
       <c r="I22" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="33"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="H23" s="33"/>
+      <c r="H23" s="30"/>
       <c r="I23" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33" t="s">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="33"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="16"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
       <c r="I24" s="16" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="37">
-      <c r="B33" s="38" t="s">
+    <row r="33" spans="2:12" ht="37">
+      <c r="B33" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-    </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="34" t="s">
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="38"/>
+      <c r="D34" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="35"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="32"/>
       <c r="I34" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:9" s="1" customFormat="1">
+    <row r="35" spans="2:12" s="1" customFormat="1">
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
@@ -4173,63 +4172,64 @@
       <c r="I35" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:9">
+      <c r="L35" s="47"/>
+    </row>
+    <row r="36" spans="2:12">
       <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D36" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
       <c r="I36" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:12">
       <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
       <c r="I37" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:12">
       <c r="C38" s="17"/>
     </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="34" t="s">
+    <row r="39" spans="2:12">
+      <c r="B39" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="38"/>
+      <c r="D39" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="35"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="32"/>
       <c r="I39" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:12">
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
@@ -4255,23 +4255,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:12">
       <c r="B41" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:12">
       <c r="B42" s="11" t="s">
         <v>15</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:12">
       <c r="B43" s="14" t="s">
         <v>55</v>
       </c>
@@ -4307,19 +4307,19 @@
       <c r="H43" s="8"/>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:12">
       <c r="C44" s="17"/>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:12">
       <c r="C45" s="17"/>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:12">
       <c r="C46" s="17"/>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:12">
       <c r="C47" s="17"/>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:12">
       <c r="C48" s="17"/>
     </row>
     <row r="49" spans="2:9">
@@ -4344,31 +4344,31 @@
       <c r="C55" s="17"/>
     </row>
     <row r="58" spans="2:9">
-      <c r="B58" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="34" t="s">
+      <c r="B58" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="32"/>
+      <c r="D58" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="35"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="32"/>
       <c r="I58" s="10"/>
     </row>
     <row r="59" spans="2:9">
-      <c r="B59" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="34" t="s">
+      <c r="B59" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="35"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="32"/>
       <c r="I59" s="10"/>
     </row>
     <row r="60" spans="2:9">
@@ -4400,11 +4400,11 @@
     <row r="61" spans="2:9">
       <c r="B61" s="6"/>
       <c r="C61" s="7"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34"/>
       <c r="I61" s="9"/>
     </row>
     <row r="62" spans="2:9">
@@ -4437,7 +4437,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" spans="2:9">
+    <row r="65" spans="2:12">
       <c r="B65" s="13"/>
       <c r="C65" s="12"/>
       <c r="D65" s="8"/>
@@ -4447,7 +4447,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="2:9">
+    <row r="66" spans="2:12">
       <c r="B66" s="13"/>
       <c r="C66" s="12"/>
       <c r="D66" s="8"/>
@@ -4457,7 +4457,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="2:9">
+    <row r="67" spans="2:12">
       <c r="B67" s="8"/>
       <c r="C67" s="7"/>
       <c r="D67" s="8"/>
@@ -4467,7 +4467,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" spans="2:9">
+    <row r="68" spans="2:12">
       <c r="B68" s="8"/>
       <c r="C68" s="7"/>
       <c r="D68" s="8"/>
@@ -4477,7 +4477,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="2:9">
+    <row r="69" spans="2:12">
       <c r="B69" s="8"/>
       <c r="C69" s="7"/>
       <c r="D69" s="8"/>
@@ -4487,7 +4487,7 @@
       <c r="H69" s="8"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9">
+    <row r="70" spans="2:12">
       <c r="B70" s="8"/>
       <c r="C70" s="7"/>
       <c r="D70" s="8"/>
@@ -4497,35 +4497,35 @@
       <c r="H70" s="8"/>
       <c r="I70" s="9"/>
     </row>
-    <row r="74" spans="2:9">
-      <c r="B74" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C74" s="35"/>
-      <c r="D74" s="34" t="s">
+    <row r="74" spans="2:12">
+      <c r="B74" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="32"/>
+      <c r="D74" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="35"/>
+      <c r="E74" s="33"/>
+      <c r="F74" s="33"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="32"/>
       <c r="I74" s="10"/>
     </row>
-    <row r="75" spans="2:9">
-      <c r="B75" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C75" s="35"/>
-      <c r="D75" s="34" t="s">
+    <row r="75" spans="2:12">
+      <c r="B75" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="32"/>
+      <c r="D75" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E75" s="36"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="35"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
+      <c r="H75" s="32"/>
       <c r="I75" s="10"/>
     </row>
-    <row r="76" spans="2:9" s="1" customFormat="1">
+    <row r="76" spans="2:12" s="1" customFormat="1">
       <c r="B76" s="8" t="s">
         <v>2</v>
       </c>
@@ -4550,26 +4550,27 @@
       <c r="I76" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="2:9">
+      <c r="L76" s="47"/>
+    </row>
+    <row r="77" spans="2:12">
       <c r="B77" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D77" s="37" t="s">
+      <c r="D77" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="34"/>
       <c r="I77" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="2:9">
+    <row r="78" spans="2:12">
       <c r="B78" s="11" t="s">
         <v>15</v>
       </c>
@@ -4589,7 +4590,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="2:9">
+    <row r="79" spans="2:12">
       <c r="B79" s="11" t="s">
         <v>15</v>
       </c>
@@ -4609,7 +4610,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="2:9">
+    <row r="80" spans="2:12">
       <c r="B80" s="11" t="s">
         <v>15</v>
       </c>
@@ -4890,34 +4891,34 @@
       </c>
     </row>
     <row r="95" spans="2:9">
-      <c r="B95" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C95" s="35"/>
-      <c r="D95" s="34" t="s">
+      <c r="B95" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C95" s="32"/>
+      <c r="D95" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="36"/>
-      <c r="H95" s="35"/>
+      <c r="E95" s="33"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="32"/>
       <c r="I95" s="10"/>
     </row>
     <row r="96" spans="2:9">
-      <c r="B96" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C96" s="35"/>
-      <c r="D96" s="34" t="s">
+      <c r="B96" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" s="32"/>
+      <c r="D96" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="36"/>
-      <c r="F96" s="36"/>
-      <c r="G96" s="36"/>
-      <c r="H96" s="35"/>
+      <c r="E96" s="33"/>
+      <c r="F96" s="33"/>
+      <c r="G96" s="33"/>
+      <c r="H96" s="32"/>
       <c r="I96" s="10"/>
     </row>
-    <row r="97" spans="2:9" s="1" customFormat="1">
+    <row r="97" spans="2:12" s="1" customFormat="1">
       <c r="B97" s="8" t="s">
         <v>2</v>
       </c>
@@ -4942,26 +4943,27 @@
       <c r="I97" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="2:9">
+      <c r="L97" s="47"/>
+    </row>
+    <row r="98" spans="2:12">
       <c r="B98" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D98" s="37" t="s">
+      <c r="D98" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
-      <c r="G98" s="37"/>
-      <c r="H98" s="37"/>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="34"/>
+      <c r="H98" s="34"/>
       <c r="I98" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="99" spans="2:9">
+    <row r="99" spans="2:12">
       <c r="B99" s="11" t="s">
         <v>15</v>
       </c>
@@ -4981,7 +4983,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="2:9">
+    <row r="100" spans="2:12">
       <c r="B100" s="14" t="s">
         <v>55</v>
       </c>
@@ -4999,7 +5001,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="2:9">
+    <row r="101" spans="2:12">
       <c r="B101" s="13" t="s">
         <v>20</v>
       </c>
@@ -5019,35 +5021,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="2:9">
-      <c r="B104" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="35"/>
-      <c r="D104" s="34" t="s">
+    <row r="104" spans="2:12">
+      <c r="B104" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="32"/>
+      <c r="D104" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E104" s="36"/>
-      <c r="F104" s="36"/>
-      <c r="G104" s="36"/>
-      <c r="H104" s="35"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="33"/>
+      <c r="G104" s="33"/>
+      <c r="H104" s="32"/>
       <c r="I104" s="10"/>
     </row>
-    <row r="105" spans="2:9">
-      <c r="B105" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C105" s="35"/>
-      <c r="D105" s="34" t="s">
+    <row r="105" spans="2:12">
+      <c r="B105" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C105" s="32"/>
+      <c r="D105" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E105" s="36"/>
-      <c r="F105" s="36"/>
-      <c r="G105" s="36"/>
-      <c r="H105" s="35"/>
+      <c r="E105" s="33"/>
+      <c r="F105" s="33"/>
+      <c r="G105" s="33"/>
+      <c r="H105" s="32"/>
       <c r="I105" s="10"/>
     </row>
-    <row r="106" spans="2:9" s="1" customFormat="1">
+    <row r="106" spans="2:12" s="1" customFormat="1">
       <c r="B106" s="8" t="s">
         <v>2</v>
       </c>
@@ -5072,26 +5074,27 @@
       <c r="I106" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="2:9">
+      <c r="L106" s="47"/>
+    </row>
+    <row r="107" spans="2:12">
       <c r="B107" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D107" s="37" t="s">
+      <c r="D107" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="E107" s="37"/>
-      <c r="F107" s="37"/>
-      <c r="G107" s="37"/>
-      <c r="H107" s="37"/>
+      <c r="E107" s="34"/>
+      <c r="F107" s="34"/>
+      <c r="G107" s="34"/>
+      <c r="H107" s="34"/>
       <c r="I107" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="2:9">
+    <row r="108" spans="2:12">
       <c r="B108" s="11" t="s">
         <v>15</v>
       </c>
@@ -5111,7 +5114,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="2:9">
+    <row r="109" spans="2:12">
       <c r="B109" s="11" t="s">
         <v>15</v>
       </c>
@@ -5131,7 +5134,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="2:9">
+    <row r="110" spans="2:12">
       <c r="B110" s="14" t="s">
         <v>55</v>
       </c>
@@ -5149,7 +5152,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="2:9">
+    <row r="111" spans="2:12">
       <c r="B111" s="13" t="s">
         <v>20</v>
       </c>
@@ -5169,35 +5172,35 @@
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="2:9">
-      <c r="B114" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C114" s="35"/>
-      <c r="D114" s="34" t="s">
+    <row r="114" spans="2:12">
+      <c r="B114" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C114" s="32"/>
+      <c r="D114" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E114" s="36"/>
-      <c r="F114" s="36"/>
-      <c r="G114" s="36"/>
-      <c r="H114" s="35"/>
+      <c r="E114" s="33"/>
+      <c r="F114" s="33"/>
+      <c r="G114" s="33"/>
+      <c r="H114" s="32"/>
       <c r="I114" s="10"/>
     </row>
-    <row r="115" spans="2:9">
-      <c r="B115" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C115" s="35"/>
-      <c r="D115" s="34" t="s">
+    <row r="115" spans="2:12">
+      <c r="B115" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C115" s="32"/>
+      <c r="D115" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E115" s="36"/>
-      <c r="F115" s="36"/>
-      <c r="G115" s="36"/>
-      <c r="H115" s="35"/>
+      <c r="E115" s="33"/>
+      <c r="F115" s="33"/>
+      <c r="G115" s="33"/>
+      <c r="H115" s="32"/>
       <c r="I115" s="10"/>
     </row>
-    <row r="116" spans="2:9" s="1" customFormat="1">
+    <row r="116" spans="2:12" s="1" customFormat="1">
       <c r="B116" s="8" t="s">
         <v>2</v>
       </c>
@@ -5222,26 +5225,27 @@
       <c r="I116" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="2:9">
+      <c r="L116" s="47"/>
+    </row>
+    <row r="117" spans="2:12">
       <c r="B117" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D117" s="37" t="s">
+      <c r="D117" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E117" s="37"/>
-      <c r="F117" s="37"/>
-      <c r="G117" s="37"/>
-      <c r="H117" s="37"/>
+      <c r="E117" s="34"/>
+      <c r="F117" s="34"/>
+      <c r="G117" s="34"/>
+      <c r="H117" s="34"/>
       <c r="I117" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="2:9">
+    <row r="118" spans="2:12">
       <c r="B118" s="11" t="s">
         <v>15</v>
       </c>
@@ -5261,7 +5265,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="119" spans="2:9">
+    <row r="119" spans="2:12">
       <c r="B119" s="11" t="s">
         <v>15</v>
       </c>
@@ -5281,7 +5285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="2:9">
+    <row r="120" spans="2:12">
       <c r="B120" s="11" t="s">
         <v>15</v>
       </c>
@@ -5301,7 +5305,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="121" spans="2:9">
+    <row r="121" spans="2:12">
       <c r="B121" s="11" t="s">
         <v>15</v>
       </c>
@@ -5321,7 +5325,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="122" spans="2:9">
+    <row r="122" spans="2:12">
       <c r="B122" s="14" t="s">
         <v>55</v>
       </c>
@@ -5339,7 +5343,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="123" spans="2:9">
+    <row r="123" spans="2:12">
       <c r="B123" s="13" t="s">
         <v>20</v>
       </c>
@@ -5359,7 +5363,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="2:9">
+    <row r="124" spans="2:12">
       <c r="B124" s="13" t="s">
         <v>20</v>
       </c>
@@ -5383,35 +5387,35 @@
         <v>76</v>
       </c>
     </row>
-    <row r="127" spans="2:9">
-      <c r="B127" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" s="35"/>
-      <c r="D127" s="34" t="s">
+    <row r="127" spans="2:12">
+      <c r="B127" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C127" s="32"/>
+      <c r="D127" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E127" s="36"/>
-      <c r="F127" s="36"/>
-      <c r="G127" s="36"/>
-      <c r="H127" s="35"/>
+      <c r="E127" s="33"/>
+      <c r="F127" s="33"/>
+      <c r="G127" s="33"/>
+      <c r="H127" s="32"/>
       <c r="I127" s="10"/>
     </row>
-    <row r="128" spans="2:9">
-      <c r="B128" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C128" s="35"/>
-      <c r="D128" s="34" t="s">
+    <row r="128" spans="2:12">
+      <c r="B128" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C128" s="32"/>
+      <c r="D128" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E128" s="36"/>
-      <c r="F128" s="36"/>
-      <c r="G128" s="36"/>
-      <c r="H128" s="35"/>
+      <c r="E128" s="33"/>
+      <c r="F128" s="33"/>
+      <c r="G128" s="33"/>
+      <c r="H128" s="32"/>
       <c r="I128" s="10"/>
     </row>
-    <row r="129" spans="2:9" s="1" customFormat="1">
+    <row r="129" spans="2:12" s="1" customFormat="1">
       <c r="B129" s="8" t="s">
         <v>2</v>
       </c>
@@ -5436,26 +5440,27 @@
       <c r="I129" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="2:9">
+      <c r="L129" s="47"/>
+    </row>
+    <row r="130" spans="2:12">
       <c r="B130" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D130" s="37" t="s">
+      <c r="D130" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="E130" s="37"/>
-      <c r="F130" s="37"/>
-      <c r="G130" s="37"/>
-      <c r="H130" s="37"/>
+      <c r="E130" s="34"/>
+      <c r="F130" s="34"/>
+      <c r="G130" s="34"/>
+      <c r="H130" s="34"/>
       <c r="I130" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="131" spans="2:9">
+    <row r="131" spans="2:12">
       <c r="B131" s="11" t="s">
         <v>15</v>
       </c>
@@ -5475,7 +5480,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="132" spans="2:9">
+    <row r="132" spans="2:12">
       <c r="B132" s="11" t="s">
         <v>15</v>
       </c>
@@ -5495,7 +5500,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="133" spans="2:9">
+    <row r="133" spans="2:12">
       <c r="B133" s="14" t="s">
         <v>55</v>
       </c>
@@ -5513,7 +5518,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="2:9">
+    <row r="134" spans="2:12">
       <c r="B134" s="13" t="s">
         <v>20</v>
       </c>
@@ -5533,35 +5538,35 @@
         <v>81</v>
       </c>
     </row>
-    <row r="137" spans="2:9">
-      <c r="B137" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C137" s="35"/>
-      <c r="D137" s="34" t="s">
+    <row r="137" spans="2:12">
+      <c r="B137" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C137" s="32"/>
+      <c r="D137" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E137" s="36"/>
-      <c r="F137" s="36"/>
-      <c r="G137" s="36"/>
-      <c r="H137" s="35"/>
+      <c r="E137" s="33"/>
+      <c r="F137" s="33"/>
+      <c r="G137" s="33"/>
+      <c r="H137" s="32"/>
       <c r="I137" s="10"/>
     </row>
-    <row r="138" spans="2:9">
-      <c r="B138" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C138" s="35"/>
-      <c r="D138" s="34" t="s">
+    <row r="138" spans="2:12">
+      <c r="B138" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C138" s="32"/>
+      <c r="D138" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-      <c r="G138" s="36"/>
-      <c r="H138" s="35"/>
+      <c r="E138" s="33"/>
+      <c r="F138" s="33"/>
+      <c r="G138" s="33"/>
+      <c r="H138" s="32"/>
       <c r="I138" s="10"/>
     </row>
-    <row r="139" spans="2:9" s="1" customFormat="1">
+    <row r="139" spans="2:12" s="1" customFormat="1">
       <c r="B139" s="8" t="s">
         <v>2</v>
       </c>
@@ -5586,26 +5591,27 @@
       <c r="I139" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="2:9">
+      <c r="L139" s="47"/>
+    </row>
+    <row r="140" spans="2:12">
       <c r="B140" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D140" s="37" t="s">
+      <c r="D140" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="E140" s="37"/>
-      <c r="F140" s="37"/>
-      <c r="G140" s="37"/>
-      <c r="H140" s="37"/>
+      <c r="E140" s="34"/>
+      <c r="F140" s="34"/>
+      <c r="G140" s="34"/>
+      <c r="H140" s="34"/>
       <c r="I140" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="141" spans="2:9">
+    <row r="141" spans="2:12">
       <c r="B141" s="11" t="s">
         <v>15</v>
       </c>
@@ -5625,7 +5631,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="142" spans="2:9">
+    <row r="142" spans="2:12">
       <c r="B142" s="11" t="s">
         <v>15</v>
       </c>
@@ -5645,7 +5651,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="143" spans="2:9">
+    <row r="143" spans="2:12">
       <c r="B143" s="11" t="s">
         <v>15</v>
       </c>
@@ -5665,7 +5671,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="144" spans="2:9">
+    <row r="144" spans="2:12">
       <c r="B144" s="14" t="s">
         <v>55</v>
       </c>
@@ -5683,7 +5689,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="145" spans="2:9">
+    <row r="145" spans="2:12">
       <c r="B145" s="13" t="s">
         <v>20</v>
       </c>
@@ -5703,7 +5709,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="146" spans="2:9">
+    <row r="146" spans="2:12">
       <c r="B146" s="13" t="s">
         <v>20</v>
       </c>
@@ -5727,7 +5733,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="147" spans="2:9">
+    <row r="147" spans="2:12">
       <c r="B147" s="13" t="s">
         <v>20</v>
       </c>
@@ -5747,35 +5753,35 @@
         <v>92</v>
       </c>
     </row>
-    <row r="150" spans="2:9">
-      <c r="B150" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C150" s="35"/>
-      <c r="D150" s="34" t="s">
+    <row r="150" spans="2:12">
+      <c r="B150" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C150" s="32"/>
+      <c r="D150" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E150" s="36"/>
-      <c r="F150" s="36"/>
-      <c r="G150" s="36"/>
-      <c r="H150" s="35"/>
+      <c r="E150" s="33"/>
+      <c r="F150" s="33"/>
+      <c r="G150" s="33"/>
+      <c r="H150" s="32"/>
       <c r="I150" s="10"/>
     </row>
-    <row r="151" spans="2:9">
-      <c r="B151" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C151" s="35"/>
-      <c r="D151" s="34" t="s">
+    <row r="151" spans="2:12">
+      <c r="B151" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C151" s="32"/>
+      <c r="D151" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E151" s="36"/>
-      <c r="F151" s="36"/>
-      <c r="G151" s="36"/>
-      <c r="H151" s="35"/>
+      <c r="E151" s="33"/>
+      <c r="F151" s="33"/>
+      <c r="G151" s="33"/>
+      <c r="H151" s="32"/>
       <c r="I151" s="10"/>
     </row>
-    <row r="152" spans="2:9" s="1" customFormat="1">
+    <row r="152" spans="2:12" s="1" customFormat="1">
       <c r="B152" s="8" t="s">
         <v>2</v>
       </c>
@@ -5800,26 +5806,27 @@
       <c r="I152" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="2:9">
+      <c r="L152" s="47"/>
+    </row>
+    <row r="153" spans="2:12">
       <c r="B153" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C153" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D153" s="37" t="s">
+      <c r="D153" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="E153" s="37"/>
-      <c r="F153" s="37"/>
-      <c r="G153" s="37"/>
-      <c r="H153" s="37"/>
+      <c r="E153" s="34"/>
+      <c r="F153" s="34"/>
+      <c r="G153" s="34"/>
+      <c r="H153" s="34"/>
       <c r="I153" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="154" spans="2:9">
+    <row r="154" spans="2:12">
       <c r="B154" s="11" t="s">
         <v>15</v>
       </c>
@@ -5839,7 +5846,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="155" spans="2:9">
+    <row r="155" spans="2:12">
       <c r="B155" s="11" t="s">
         <v>15</v>
       </c>
@@ -5859,7 +5866,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="2:9">
+    <row r="156" spans="2:12">
       <c r="B156" s="11" t="s">
         <v>15</v>
       </c>
@@ -5879,7 +5886,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="157" spans="2:9">
+    <row r="157" spans="2:12">
       <c r="B157" s="11" t="s">
         <v>15</v>
       </c>
@@ -5899,7 +5906,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="158" spans="2:9">
+    <row r="158" spans="2:12">
       <c r="B158" s="13" t="s">
         <v>20</v>
       </c>
@@ -5921,7 +5928,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="2:9">
+    <row r="159" spans="2:12">
       <c r="B159" s="13" t="s">
         <v>20</v>
       </c>
@@ -5945,7 +5952,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="160" spans="2:9">
+    <row r="160" spans="2:12">
       <c r="B160" s="13" t="s">
         <v>20</v>
       </c>
@@ -6040,8 +6047,8 @@
       </c>
     </row>
     <row r="191" spans="11:15">
-      <c r="L191" s="3" t="s">
-        <v>449</v>
+      <c r="L191" s="46" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="192" spans="11:15">
@@ -6049,7 +6056,7 @@
         <v>409</v>
       </c>
       <c r="O192" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193" spans="5:15">
@@ -6057,12 +6064,12 @@
         <v>408</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="5:15">
       <c r="K194" s="3" t="s">
-        <v>410</v>
+        <v>486</v>
       </c>
       <c r="O194" s="3">
         <v>2</v>
@@ -6070,24 +6077,24 @@
     </row>
     <row r="196" spans="5:15">
       <c r="K196" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="197" spans="5:15">
       <c r="K197" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="198" spans="5:15">
       <c r="E198" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F198" s="39" t="s">
+      <c r="F198" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="G198" s="40"/>
+      <c r="G198" s="37"/>
       <c r="K198" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="199" spans="5:15">
@@ -6103,7 +6110,7 @@
     </row>
     <row r="200" spans="5:15">
       <c r="K200" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="201" spans="5:15">
@@ -6115,7 +6122,7 @@
       </c>
       <c r="G201" s="8"/>
       <c r="K201" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="202" spans="5:15">
@@ -6129,29 +6136,29 @@
         <v>179</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="203" spans="5:15">
       <c r="K203" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="204" spans="5:15">
       <c r="K204" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="205" spans="5:15">
       <c r="E205" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F205" s="39" t="s">
+      <c r="F205" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="G205" s="40"/>
+      <c r="G205" s="37"/>
       <c r="K205" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="206" spans="5:15">
@@ -6163,7 +6170,7 @@
       </c>
       <c r="G206" s="8"/>
       <c r="K206" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="207" spans="5:15">
@@ -6184,27 +6191,27 @@
       </c>
       <c r="G208" s="8"/>
       <c r="K208" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="209" spans="5:12">
       <c r="K209" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="210" spans="5:12">
       <c r="E210" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F210" s="39" t="s">
+      <c r="F210" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="G210" s="40"/>
-      <c r="K210" s="28" t="s">
-        <v>423</v>
-      </c>
-      <c r="L210" s="29" t="s">
-        <v>456</v>
+      <c r="G210" s="37"/>
+      <c r="K210" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="L210" s="48" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="211" spans="5:12">
@@ -6216,10 +6223,10 @@
       </c>
       <c r="G211" s="8"/>
       <c r="K211" s="23" t="s">
-        <v>424</v>
-      </c>
-      <c r="L211" s="27" t="s">
-        <v>457</v>
+        <v>423</v>
+      </c>
+      <c r="L211" s="49" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="212" spans="5:12">
@@ -6231,10 +6238,10 @@
       </c>
       <c r="G212" s="8"/>
       <c r="K212" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="L212" s="27" t="s">
-        <v>458</v>
+        <v>444</v>
+      </c>
+      <c r="L212" s="49" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="5:12">
@@ -6246,22 +6253,22 @@
       </c>
       <c r="G213" s="8"/>
       <c r="K213" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="L213" s="27" t="s">
-        <v>459</v>
+        <v>424</v>
+      </c>
+      <c r="L213" s="49" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="215" spans="5:12">
       <c r="E215" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="F215" s="39" t="s">
+      <c r="F215" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="G215" s="40"/>
+      <c r="G215" s="37"/>
       <c r="K215" s="3" t="s">
-        <v>426</v>
+        <v>487</v>
       </c>
     </row>
     <row r="216" spans="5:12">
@@ -6275,7 +6282,7 @@
         <v>182</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>427</v>
+        <v>488</v>
       </c>
     </row>
     <row r="217" spans="5:12">
@@ -6288,6 +6295,12 @@
       <c r="G217" s="8" t="s">
         <v>183</v>
       </c>
+      <c r="K217" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="L217" s="50" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="218" spans="5:12">
       <c r="E218" s="8" t="s">
@@ -6300,15 +6313,18 @@
         <v>184</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>430</v>
+        <v>496</v>
+      </c>
+      <c r="L218" s="50" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="219" spans="5:12">
-      <c r="K219" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="L219" s="31" t="s">
-        <v>460</v>
+      <c r="K219" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="L219" s="50" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="220" spans="5:12">
@@ -6333,7 +6349,7 @@
         <v>159</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="222" spans="5:12">
@@ -6347,25 +6363,23 @@
         <v>159</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="223" spans="5:12">
-      <c r="K223" s="3" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
     </row>
     <row r="224" spans="5:12">
       <c r="K224" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="225" spans="5:11">
-      <c r="K225" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="226" spans="5:11">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="225" spans="5:12">
+      <c r="K225" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="L225" s="51" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="226" spans="5:12">
       <c r="E226" s="11" t="s">
         <v>180</v>
       </c>
@@ -6376,7 +6390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="5:11">
+    <row r="227" spans="5:12">
       <c r="E227" s="8"/>
       <c r="F227" s="8" t="s">
         <v>117</v>
@@ -6385,10 +6399,10 @@
         <v>31</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="228" spans="5:11">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="228" spans="5:12">
       <c r="E228" s="8"/>
       <c r="F228" s="8" t="s">
         <v>120</v>
@@ -6397,10 +6411,10 @@
         <v>31</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="229" spans="5:11">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="229" spans="5:12">
       <c r="E229" s="8"/>
       <c r="F229" s="8" t="s">
         <v>121</v>
@@ -6409,10 +6423,10 @@
         <v>31</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="230" spans="5:11">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="230" spans="5:12">
       <c r="E230" s="8"/>
       <c r="F230" s="8" t="s">
         <v>122</v>
@@ -6421,15 +6435,15 @@
         <v>28</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="231" spans="5:11">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="231" spans="5:12">
       <c r="K231" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="232" spans="5:11">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="232" spans="5:12">
       <c r="E232" s="11" t="s">
         <v>167</v>
       </c>
@@ -6440,7 +6454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="5:11">
+    <row r="233" spans="5:12">
       <c r="E233" s="8"/>
       <c r="F233" s="8" t="s">
         <v>130</v>
@@ -6449,10 +6463,10 @@
         <v>31</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="234" spans="5:11">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="234" spans="5:12">
       <c r="E234" s="8"/>
       <c r="F234" s="8" t="s">
         <v>131</v>
@@ -6461,15 +6475,15 @@
         <v>31</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="235" spans="5:11">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="235" spans="5:12">
       <c r="K235" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="236" spans="5:11">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="236" spans="5:12">
       <c r="E236" s="11" t="s">
         <v>169</v>
       </c>
@@ -6480,10 +6494,10 @@
         <v>5</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="237" spans="5:11">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="237" spans="5:12">
       <c r="E237" s="8"/>
       <c r="F237" s="8" t="s">
         <v>135</v>
@@ -6491,8 +6505,11 @@
       <c r="G237" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="238" spans="5:11">
+      <c r="K237" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="238" spans="5:12">
       <c r="E238" s="8"/>
       <c r="F238" s="8" t="s">
         <v>130</v>
@@ -6500,11 +6517,8 @@
       <c r="G238" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K238" s="3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="239" spans="5:11">
+    </row>
+    <row r="239" spans="5:12">
       <c r="E239" s="8"/>
       <c r="F239" s="8" t="s">
         <v>136</v>
@@ -6513,16 +6527,19 @@
         <v>31</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="240" spans="5:11">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="240" spans="5:12">
       <c r="E240" s="8"/>
       <c r="F240" s="8" t="s">
         <v>137</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>28</v>
+      </c>
+      <c r="K240" s="3" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="241" spans="5:11">
@@ -6533,10 +6550,28 @@
       <c r="G241" s="8" t="s">
         <v>31</v>
       </c>
+      <c r="K241" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="242" spans="5:11">
+      <c r="K242" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="244" spans="5:11">
+      <c r="K244" s="3" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="245" spans="5:11">
       <c r="K245" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="248" spans="5:11">
+      <c r="K248" s="3" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -6655,7 +6690,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6664,165 +6698,165 @@
   <dimension ref="B2:B42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="16384" width="10.625" style="43"/>
+    <col min="1" max="16384" width="10.625" style="40"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2" ht="23">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="39" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="23">
+      <c r="B3" s="39" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="23">
+      <c r="B4" s="39" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="23">
+      <c r="B7" s="39" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="23">
+      <c r="B8" s="39" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="23">
-      <c r="B3" s="42" t="s">
+    <row r="9" spans="2:2" ht="23">
+      <c r="B9" s="39" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="23">
-      <c r="B4" s="42" t="s">
+    <row r="10" spans="2:2" ht="23">
+      <c r="B10" s="39"/>
+    </row>
+    <row r="11" spans="2:2" ht="23">
+      <c r="B11" s="39" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="23">
-      <c r="B7" s="42" t="s">
+    <row r="12" spans="2:2" ht="23">
+      <c r="B12" s="41" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="23">
-      <c r="B8" s="42" t="s">
+    <row r="13" spans="2:2" ht="23">
+      <c r="B13" s="41" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="23">
-      <c r="B9" s="42" t="s">
+    <row r="14" spans="2:2" ht="23">
+      <c r="B14" s="41" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="23">
-      <c r="B10" s="42"/>
-    </row>
-    <row r="11" spans="2:2" ht="23">
-      <c r="B11" s="42" t="s">
+    <row r="15" spans="2:2" ht="23">
+      <c r="B15" s="41" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="23">
-      <c r="B12" s="44" t="s">
+    <row r="16" spans="2:2" ht="23">
+      <c r="B16" s="41" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="23">
-      <c r="B13" s="44" t="s">
+    <row r="20" spans="2:2" ht="23">
+      <c r="B20" s="39" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="23">
-      <c r="B14" s="44" t="s">
+    <row r="21" spans="2:2" ht="23">
+      <c r="B21" s="41" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="23">
-      <c r="B15" s="44" t="s">
+    <row r="22" spans="2:2" ht="23">
+      <c r="B22" s="41" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="23">
-      <c r="B16" s="44" t="s">
+    <row r="23" spans="2:2" ht="23">
+      <c r="B23" s="41" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="23">
-      <c r="B20" s="42" t="s">
+    <row r="24" spans="2:2" ht="23">
+      <c r="B24" s="41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="23">
+      <c r="B27" s="39" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="23">
-      <c r="B21" s="44" t="s">
+    <row r="28" spans="2:2" ht="23">
+      <c r="B28" s="41" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="23">
-      <c r="B22" s="44" t="s">
+    <row r="29" spans="2:2" ht="23">
+      <c r="B29" s="41" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="23">
-      <c r="B23" s="44" t="s">
+    <row r="30" spans="2:2" ht="23">
+      <c r="B30" s="41" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="23">
-      <c r="B24" s="44" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" ht="23">
-      <c r="B27" s="42" t="s">
+    <row r="31" spans="2:2" ht="23">
+      <c r="B31" s="41" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="23">
-      <c r="B28" s="44" t="s">
+    <row r="32" spans="2:2" ht="23">
+      <c r="B32" s="41" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="23">
-      <c r="B29" s="44" t="s">
+    <row r="33" spans="2:2" ht="23">
+      <c r="B33" s="41" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="23">
-      <c r="B30" s="44" t="s">
+    <row r="34" spans="2:2" ht="23">
+      <c r="B34" s="39" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="23">
-      <c r="B31" s="44" t="s">
+    <row r="35" spans="2:2" ht="23">
+      <c r="B35" s="39" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="23">
-      <c r="B32" s="44" t="s">
+    <row r="36" spans="2:2" ht="23">
+      <c r="B36" s="41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" ht="23">
+      <c r="B38" s="41" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="23">
+      <c r="B39" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="23">
+      <c r="B40" s="41" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="23">
+      <c r="B42" s="39" t="s">
         <v>482</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="23">
-      <c r="B33" s="44" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="23">
-      <c r="B34" s="42" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="23">
-      <c r="B35" s="42" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="23">
-      <c r="B36" s="44" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="23">
-      <c r="B38" s="44" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="23">
-      <c r="B39" s="44" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="23">
-      <c r="B40" s="44" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="23">
-      <c r="B42" s="42" t="s">
-        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -6900,7 +6934,7 @@
         <v>136</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="W2" s="21" t="s">
         <v>406</v>
@@ -6960,7 +6994,7 @@
         <v>330</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T4" s="19" t="s">
         <v>287</v>
@@ -7029,7 +7063,7 @@
         <v>330</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T5" s="19" t="s">
         <v>289</v>
@@ -7098,7 +7132,7 @@
         <v>330</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T6" s="19" t="s">
         <v>292</v>
@@ -7167,7 +7201,7 @@
         <v>330</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T7" s="19" t="s">
         <v>293</v>
@@ -7236,7 +7270,7 @@
         <v>330</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T8" s="19" t="s">
         <v>295</v>
@@ -7305,7 +7339,7 @@
         <v>330</v>
       </c>
       <c r="S9" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T9" s="19" t="s">
         <v>297</v>
@@ -7374,7 +7408,7 @@
         <v>330</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T10" s="19" t="s">
         <v>299</v>
@@ -7443,7 +7477,7 @@
         <v>330</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T11" s="19" t="s">
         <v>301</v>
@@ -7512,7 +7546,7 @@
         <v>330</v>
       </c>
       <c r="S12" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T12" s="19" t="s">
         <v>303</v>
@@ -7581,7 +7615,7 @@
         <v>330</v>
       </c>
       <c r="S13" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T13" s="19" t="s">
         <v>305</v>
@@ -7650,7 +7684,7 @@
         <v>330</v>
       </c>
       <c r="S14" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T14" s="19" t="s">
         <v>307</v>
@@ -7719,7 +7753,7 @@
         <v>330</v>
       </c>
       <c r="S15" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T15" s="19" t="s">
         <v>309</v>
@@ -7788,7 +7822,7 @@
         <v>330</v>
       </c>
       <c r="S16" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T16" s="19" t="s">
         <v>311</v>
@@ -7857,7 +7891,7 @@
         <v>330</v>
       </c>
       <c r="S17" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T17" s="19" t="s">
         <v>313</v>
@@ -7926,7 +7960,7 @@
         <v>330</v>
       </c>
       <c r="S18" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T18" s="19" t="s">
         <v>315</v>
@@ -7995,7 +8029,7 @@
         <v>330</v>
       </c>
       <c r="S19" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T19" s="19" t="s">
         <v>317</v>
@@ -8064,7 +8098,7 @@
         <v>330</v>
       </c>
       <c r="S20" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T20" s="19" t="s">
         <v>321</v>
@@ -8133,7 +8167,7 @@
         <v>330</v>
       </c>
       <c r="S21" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T21" s="19" t="s">
         <v>320</v>
@@ -8202,7 +8236,7 @@
         <v>330</v>
       </c>
       <c r="S22" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T22" s="19" t="s">
         <v>323</v>
@@ -8271,7 +8305,7 @@
         <v>330</v>
       </c>
       <c r="S23" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T23" s="19" t="s">
         <v>325</v>
@@ -8340,7 +8374,7 @@
         <v>330</v>
       </c>
       <c r="S24" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T24" s="19" t="s">
         <v>327</v>
@@ -8409,7 +8443,7 @@
         <v>330</v>
       </c>
       <c r="S25" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T25" s="19" t="s">
         <v>328</v>
@@ -8463,7 +8497,7 @@
         <v>330</v>
       </c>
       <c r="S26" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T26" s="19" t="s">
         <v>287</v>
@@ -8517,7 +8551,7 @@
         <v>330</v>
       </c>
       <c r="S27" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T27" s="19" t="s">
         <v>289</v>
@@ -8571,7 +8605,7 @@
         <v>330</v>
       </c>
       <c r="S28" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T28" s="19" t="s">
         <v>292</v>
@@ -8625,7 +8659,7 @@
         <v>330</v>
       </c>
       <c r="S29" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T29" s="19" t="s">
         <v>293</v>
@@ -8679,7 +8713,7 @@
         <v>330</v>
       </c>
       <c r="S30" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T30" s="19" t="s">
         <v>295</v>
@@ -8733,7 +8767,7 @@
         <v>330</v>
       </c>
       <c r="S31" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T31" s="19" t="s">
         <v>297</v>
@@ -8787,7 +8821,7 @@
         <v>330</v>
       </c>
       <c r="S32" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T32" s="19" t="s">
         <v>299</v>
@@ -8841,7 +8875,7 @@
         <v>330</v>
       </c>
       <c r="S33" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T33" s="19" t="s">
         <v>301</v>
@@ -8895,7 +8929,7 @@
         <v>330</v>
       </c>
       <c r="S34" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T34" s="19" t="s">
         <v>303</v>
@@ -8949,7 +8983,7 @@
         <v>330</v>
       </c>
       <c r="S35" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T35" s="19" t="s">
         <v>305</v>
@@ -8976,7 +9010,7 @@
         <v>330</v>
       </c>
       <c r="S36" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T36" s="19" t="s">
         <v>307</v>
@@ -8998,38 +9032,38 @@
       </c>
     </row>
     <row r="37" spans="2:30">
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="46" t="s">
-        <v>487</v>
-      </c>
-      <c r="D37" s="47" t="s">
+      <c r="C37" s="43" t="s">
+        <v>483</v>
+      </c>
+      <c r="D37" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="E37" s="46" t="s">
-        <v>488</v>
-      </c>
-      <c r="F37" s="47" t="s">
+      <c r="E37" s="43" t="s">
+        <v>484</v>
+      </c>
+      <c r="F37" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="G37" s="46" t="s">
-        <v>489</v>
-      </c>
-      <c r="H37" s="47" t="s">
+      <c r="G37" s="43" t="s">
+        <v>485</v>
+      </c>
+      <c r="H37" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I37" s="45">
-        <v>0</v>
-      </c>
-      <c r="J37" s="45" t="s">
+      <c r="I37" s="42">
+        <v>0</v>
+      </c>
+      <c r="J37" s="42" t="s">
         <v>187</v>
       </c>
       <c r="R37" s="18" t="s">
         <v>330</v>
       </c>
       <c r="S37" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T37" s="19" t="s">
         <v>287</v>
@@ -9055,7 +9089,7 @@
         <v>330</v>
       </c>
       <c r="S38" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T38" s="19" t="s">
         <v>289</v>
@@ -9081,7 +9115,7 @@
         <v>330</v>
       </c>
       <c r="S39" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T39" s="19" t="s">
         <v>292</v>
@@ -9107,7 +9141,7 @@
         <v>330</v>
       </c>
       <c r="S40" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T40" s="19" t="s">
         <v>293</v>
@@ -9133,7 +9167,7 @@
         <v>330</v>
       </c>
       <c r="S41" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T41" s="19" t="s">
         <v>295</v>
@@ -9159,7 +9193,7 @@
         <v>330</v>
       </c>
       <c r="S42" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T42" s="19" t="s">
         <v>297</v>
@@ -9185,7 +9219,7 @@
         <v>330</v>
       </c>
       <c r="S43" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T43" s="19" t="s">
         <v>299</v>
@@ -9211,7 +9245,7 @@
         <v>330</v>
       </c>
       <c r="S44" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T44" s="19" t="s">
         <v>301</v>
@@ -9237,7 +9271,7 @@
         <v>330</v>
       </c>
       <c r="S45" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T45" s="19" t="s">
         <v>303</v>
@@ -9263,7 +9297,7 @@
         <v>330</v>
       </c>
       <c r="S46" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T46" s="19" t="s">
         <v>305</v>
@@ -9289,7 +9323,7 @@
         <v>330</v>
       </c>
       <c r="S47" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T47" s="19" t="s">
         <v>307</v>
@@ -9315,7 +9349,7 @@
         <v>330</v>
       </c>
       <c r="S48" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T48" s="19" t="s">
         <v>309</v>
@@ -9341,7 +9375,7 @@
         <v>330</v>
       </c>
       <c r="S49" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T49" s="19" t="s">
         <v>311</v>
@@ -9367,7 +9401,7 @@
         <v>330</v>
       </c>
       <c r="S50" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T50" s="19" t="s">
         <v>313</v>
@@ -9393,7 +9427,7 @@
         <v>330</v>
       </c>
       <c r="S51" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T51" s="19" t="s">
         <v>315</v>
@@ -9419,7 +9453,7 @@
         <v>330</v>
       </c>
       <c r="S52" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T52" s="19" t="s">
         <v>317</v>
@@ -9445,7 +9479,7 @@
         <v>330</v>
       </c>
       <c r="S53" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T53" s="19" t="s">
         <v>321</v>
@@ -9471,7 +9505,7 @@
         <v>330</v>
       </c>
       <c r="S54" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T54" s="19" t="s">
         <v>320</v>
@@ -9497,7 +9531,7 @@
         <v>330</v>
       </c>
       <c r="S55" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T55" s="19" t="s">
         <v>323</v>
@@ -9523,7 +9557,7 @@
         <v>330</v>
       </c>
       <c r="S56" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T56" s="19" t="s">
         <v>325</v>
@@ -9549,7 +9583,7 @@
         <v>330</v>
       </c>
       <c r="S57" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T57" s="19" t="s">
         <v>327</v>
@@ -9575,7 +9609,7 @@
         <v>330</v>
       </c>
       <c r="S58" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T58" s="19" t="s">
         <v>328</v>
@@ -9601,7 +9635,7 @@
         <v>330</v>
       </c>
       <c r="S59" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T59" s="19" t="s">
         <v>287</v>
@@ -9627,7 +9661,7 @@
         <v>330</v>
       </c>
       <c r="S60" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T60" s="19" t="s">
         <v>289</v>
@@ -9653,7 +9687,7 @@
         <v>330</v>
       </c>
       <c r="S61" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T61" s="19" t="s">
         <v>292</v>
@@ -9679,7 +9713,7 @@
         <v>330</v>
       </c>
       <c r="S62" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T62" s="19" t="s">
         <v>293</v>
@@ -9705,7 +9739,7 @@
         <v>330</v>
       </c>
       <c r="S63" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T63" s="19" t="s">
         <v>289</v>
@@ -9731,7 +9765,7 @@
         <v>330</v>
       </c>
       <c r="S64" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T64" s="19" t="s">
         <v>292</v>
@@ -9757,7 +9791,7 @@
         <v>330</v>
       </c>
       <c r="S65" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T65" s="19" t="s">
         <v>293</v>
@@ -9783,7 +9817,7 @@
         <v>330</v>
       </c>
       <c r="S66" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T66" s="19" t="s">
         <v>295</v>
@@ -9809,7 +9843,7 @@
         <v>330</v>
       </c>
       <c r="S67" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T67" s="19" t="s">
         <v>297</v>
@@ -9835,7 +9869,7 @@
         <v>330</v>
       </c>
       <c r="S68" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T68" s="19" t="s">
         <v>299</v>
@@ -9861,7 +9895,7 @@
         <v>330</v>
       </c>
       <c r="S69" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T69" s="19" t="s">
         <v>301</v>
@@ -9887,7 +9921,7 @@
         <v>330</v>
       </c>
       <c r="S70" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T70" s="19" t="s">
         <v>303</v>
@@ -9913,7 +9947,7 @@
         <v>330</v>
       </c>
       <c r="S71" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T71" s="19" t="s">
         <v>305</v>
@@ -9939,7 +9973,7 @@
         <v>330</v>
       </c>
       <c r="S72" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T72" s="19" t="s">
         <v>307</v>
@@ -9965,7 +9999,7 @@
         <v>330</v>
       </c>
       <c r="S73" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T73" s="19" t="s">
         <v>309</v>
@@ -9991,7 +10025,7 @@
         <v>330</v>
       </c>
       <c r="S74" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T74" s="19" t="s">
         <v>311</v>
@@ -10017,7 +10051,7 @@
         <v>330</v>
       </c>
       <c r="S75" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T75" s="19" t="s">
         <v>313</v>
@@ -10043,7 +10077,7 @@
         <v>330</v>
       </c>
       <c r="S76" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T76" s="19" t="s">
         <v>315</v>
@@ -10069,7 +10103,7 @@
         <v>330</v>
       </c>
       <c r="S77" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T77" s="19" t="s">
         <v>311</v>
@@ -10095,7 +10129,7 @@
         <v>330</v>
       </c>
       <c r="S78" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="T78" s="19" t="s">
         <v>311</v>
